--- a/app/project/MDK_V5/AT32F403ARGT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F403ARGT7_WorkBench_analysis.xlsx
@@ -15,35 +15,161 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="86">
   <si>
     <t>AT32F403ARGT7_WorkBench</t>
   </si>
   <si>
-    <t>lto-llvm-e0adfd.o</t>
+    <t>at32_usart.o</t>
+  </si>
+  <si>
+    <t>pc_comm_handle.o</t>
+  </si>
+  <si>
+    <t>eventrecorder.o</t>
   </si>
   <si>
     <t>startup_at32f403a_407.o</t>
   </si>
   <si>
+    <t>adc_filter.o</t>
+  </si>
+  <si>
+    <t>key_handle.o</t>
+  </si>
+  <si>
+    <t>tmt.o</t>
+  </si>
+  <si>
+    <t>ps305d_handle.o</t>
+  </si>
+  <si>
+    <t>pid_handle.o</t>
+  </si>
+  <si>
+    <t>encoderec11.o</t>
+  </si>
+  <si>
+    <t>perf_counter.o</t>
+  </si>
+  <si>
+    <t>lcd_handle.o</t>
+  </si>
+  <si>
+    <t>flash_handle.o</t>
+  </si>
+  <si>
+    <t>work_handle.o</t>
+  </si>
+  <si>
+    <t>output_handle.o</t>
+  </si>
+  <si>
+    <t>collect_data_handle.o</t>
+  </si>
+  <si>
+    <t>ec11_handle.o</t>
+  </si>
+  <si>
+    <t>beep.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_int.o</t>
+  </si>
+  <si>
+    <t>wk_system.o</t>
+  </si>
+  <si>
+    <t>system_at32f403a_407.o</t>
+  </si>
+  <si>
+    <t>beep_handle.o</t>
+  </si>
+  <si>
+    <t>main.o</t>
+  </si>
+  <si>
+    <t>key.o</t>
+  </si>
+  <si>
+    <t>iap.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_crm.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_flash.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_tmr.o</t>
+  </si>
+  <si>
     <t>mf_w.l</t>
   </si>
   <si>
+    <t>tm1680.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_adc.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_usart.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_wk_config.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_gpio.o</t>
+  </si>
+  <si>
     <t>mc_w.l</t>
   </si>
   <si>
+    <t>at32f403a_407_misc.o</t>
+  </si>
+  <si>
+    <t>wk_gpio.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_dac.o</t>
+  </si>
+  <si>
     <t>dadd.o</t>
   </si>
   <si>
+    <t>wk_adc.o</t>
+  </si>
+  <si>
+    <t>wk_tmr.o</t>
+  </si>
+  <si>
+    <t>util_queue.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_crc.o</t>
+  </si>
+  <si>
+    <t>perfc_port_default.o</t>
+  </si>
+  <si>
     <t>dmul.o</t>
   </si>
   <si>
     <t>ddiv.o</t>
   </si>
   <si>
+    <t>wk_usart.o</t>
+  </si>
+  <si>
     <t>depilogue.o</t>
   </si>
   <si>
+    <t>wk_dac.o</t>
+  </si>
+  <si>
+    <t>at32f403a_407_wdt.o</t>
+  </si>
+  <si>
     <t>fepilogue.o</t>
   </si>
   <si>
@@ -62,6 +188,12 @@
     <t>d2f.o</t>
   </si>
   <si>
+    <t>wk_crc.o</t>
+  </si>
+  <si>
+    <t>flash.o</t>
+  </si>
+  <si>
     <t>init.o</t>
   </si>
   <si>
@@ -89,10 +221,16 @@
     <t>handlers.o</t>
   </si>
   <si>
+    <t>wk_wdt.o</t>
+  </si>
+  <si>
     <t>systick_wrapper_gnu.o</t>
   </si>
   <si>
     <t>dfltui.o</t>
+  </si>
+  <si>
+    <t>wk_debug.o</t>
   </si>
   <si>
     <t>entry9a.o</t>
@@ -224,16 +362,85 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$32</c:f>
+              <c:f>ram_percent!$A$3:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-e0adfd.o</c:v>
+                  <c:v>at32_usart.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>pc_comm_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>eventrecorder.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>startup_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="4">
+                  <c:v>adc_filter.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>key_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>tmt.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>ps305d_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>pid_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>encoderec11.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>perf_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>lcd_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>flash_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>work_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>output_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>collect_data_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>ec11_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>beep.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>at32f403a_407_int.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>wk_system.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>system_at32f403a_407.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>beep_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>key.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>iap.o</c:v>
+                </c:pt>
+                <c:pt idx="75">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -241,17 +448,86 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$32</c:f>
+              <c:f>ram_percent!$B$3:$B$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>86.01474761962891</c:v>
+                  <c:v>30.23476791381836</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.98524951934815</c:v>
-                </c:pt>
-                <c:pt idx="29">
+                  <c:v>20.99335098266602</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16.12158966064453</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>13.89605140686035</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.691138505935669</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.632650375366211</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.496946573257446</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.116976499557495</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.737006425857544</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.560591697692871</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.031347513198853</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.9906364679336548</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.7870810031890869</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.3392590582370758</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.2985479831695557</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.2714072465896606</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.2306961566209793</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.2306961566209793</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.1492739915847778</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.05428145080804825</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.05428145080804825</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.04071108624339104</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.01357036270201206</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.01357036270201206</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.01357036270201206</c:v>
+                </c:pt>
+                <c:pt idx="75">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -319,97 +595,235 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$32</c:f>
+              <c:f>flash_percent!$A$3:$A$78</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>lto-llvm-e0adfd.o</c:v>
+                  <c:v>lcd_handle.o</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>flash_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>key_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>work_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ec11_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>eventrecorder.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>at32f403a_407_crm.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>encoderec11.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>at32f403a_407_flash.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>collect_data_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>at32f403a_407_tmr.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>mf_w.l</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="12">
+                  <c:v>perf_counter.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>tmt.o</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>at32_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>tm1680.o</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>output_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>at32f403a_407_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>at32f403a_407_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>at32f403a_407_wk_config.o</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>pc_comm_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>system_at32f403a_407.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>at32f403a_407_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="24">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="25">
+                  <c:v>adc_filter.o</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>at32f403a_407_misc.o</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>startup_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="28">
+                  <c:v>wk_gpio.o</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>ps305d_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>at32f403a_407_dac.o</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="32">
+                  <c:v>wk_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>beep.o</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>wk_tmr.o</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>at32f403a_407_int.o</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>util_queue.o</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>beep_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>key.o</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>at32f403a_407_crc.o</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>perfc_port_default.o</c:v>
+                </c:pt>
+                <c:pt idx="41">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="42">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="43">
+                  <c:v>wk_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="45">
+                  <c:v>wk_dac.o</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>at32f403a_407_wdt.o</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>iap.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>wk_system.o</c:v>
+                </c:pt>
+                <c:pt idx="49">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="50">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="51">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="52">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="53">
+                  <c:v>pid_handle.o</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>dfixi.o</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="55">
                   <c:v>d2f.o</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="56">
+                  <c:v>wk_crc.o</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>flash.o</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="59">
                   <c:v>cpp_init.o</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="60">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="61">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="62">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="63">
                   <c:v>dflti.o</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="64">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="65">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="66">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="67">
+                  <c:v>wk_wdt.o</c:v>
+                </c:pt>
+                <c:pt idx="68">
                   <c:v>systick_wrapper_gnu.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="69">
                   <c:v>dfltui.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="70">
+                  <c:v>wk_debug.o</c:v>
+                </c:pt>
+                <c:pt idx="71">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="72">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="73">
                   <c:v>entry8a.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="74">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="75">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -417,98 +831,236 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$32</c:f>
+              <c:f>flash_percent!$B$3:$B$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="76"/>
                 <c:pt idx="0">
-                  <c:v>90.69330596923828</c:v>
+                  <c:v>12.93178081512451</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.899393796920776</c:v>
+                  <c:v>9.993027687072754</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.248350024223328</c:v>
+                  <c:v>6.230325698852539</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.9485670924186707</c:v>
+                  <c:v>5.184543609619141</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.7472202777862549</c:v>
+                  <c:v>4.728202342987061</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.5100785493850708</c:v>
+                  <c:v>3.507066965103149</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.4966554045677185</c:v>
+                  <c:v>3.304248571395874</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.4161166846752167</c:v>
+                  <c:v>3.13100790977478</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.2460905164480209</c:v>
+                  <c:v>3.046500444412231</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.2192442715167999</c:v>
+                  <c:v>2.873259782791138</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.2192442715167999</c:v>
+                  <c:v>2.759174346923828</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.1923980414867401</c:v>
+                  <c:v>2.738047361373901</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.1387055665254593</c:v>
+                  <c:v>2.602835178375244</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.1252824515104294</c:v>
+                  <c:v>2.378890037536621</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.1073849499225617</c:v>
+                  <c:v>2.285931587219238</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.0894874632358551</c:v>
+                  <c:v>2.159170150756836</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.08501308411359787</c:v>
+                  <c:v>2.074662446975708</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.08053871244192123</c:v>
+                  <c:v>1.926774144172669</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.08053871244192123</c:v>
+                  <c:v>1.694378137588501</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.0760643407702446</c:v>
+                  <c:v>1.470432877540588</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.07158996909856796</c:v>
+                  <c:v>1.335220694541931</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.06711559742689133</c:v>
+                  <c:v>1.28874146938324</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.06711559742689133</c:v>
+                  <c:v>1.27183997631073</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.06264122575521469</c:v>
+                  <c:v>1.27183997631073</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.05816685035824776</c:v>
+                  <c:v>1.178881525993347</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.01789749227464199</c:v>
+                  <c:v>1.153529286384583</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.01789749227464199</c:v>
+                  <c:v>1.064796209335327</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.008948746137320995</c:v>
+                  <c:v>0.8957809805870056</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.008948746137320995</c:v>
+                  <c:v>0.8408510088920593</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>0.807047963142395</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.7183149456977844</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.7056387662887573</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.6887372732162476</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.6612722873687744</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.6422580480575562</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.6169057488441467</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.5915534496307373</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.5725392699241638</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.5302854180335999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.5028204321861267</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.4859189093112946</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.4816935360431671</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.4690173864364624</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.4183128178119659</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.3929605185985565</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.2831005752086639</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.2492975294589996</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.245072141289711</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.2408467680215836</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.2323960065841675</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.2070437073707581</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.2070437073707581</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.1816914230585098</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.1352122128009796</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.1309868395328522</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.1183106899261475</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.1098599284887314</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.1056345477700234</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.1014091670513153</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.08450763672590256</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.08028225600719452</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.07605687528848648</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.07605687528848648</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.07183149456977844</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.06760610640048981</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.06338072568178177</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.06338072568178177</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.05915534496307373</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.05915534496307373</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.05492996424436569</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.03802843764424324</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.01690152660012245</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.01690152660012245</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.008450763300061226</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.008450763300061226</c:v>
+                </c:pt>
+                <c:pt idx="75">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -613,8 +1165,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H32" totalsRowCount="1">
-  <autoFilter ref="A2:H31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H78" totalsRowCount="1">
+  <autoFilter ref="A2:H77"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -630,8 +1182,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H32" totalsRowCount="1">
-  <autoFilter ref="A2:H31"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H78" totalsRowCount="1">
+  <autoFilter ref="A2:H77"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -931,7 +1483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -944,28 +1496,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -973,25 +1525,25 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>86.01474761962891</v>
+        <v>30.23476791381836</v>
       </c>
       <c r="C3" s="1">
-        <v>6298</v>
+        <v>2228</v>
       </c>
       <c r="D3" s="1">
-        <v>40539</v>
+        <v>1082</v>
       </c>
       <c r="E3" s="1">
-        <v>40070</v>
+        <v>1082</v>
       </c>
       <c r="F3" s="1">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1">
-        <v>5920</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -999,56 +1551,654 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>13.98524951934815</v>
+        <v>20.99335098266602</v>
       </c>
       <c r="C4" s="1">
+        <v>1547</v>
+      </c>
+      <c r="D4" s="1">
+        <v>610</v>
+      </c>
+      <c r="E4" s="1">
+        <v>610</v>
+      </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1547</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
+        <v>16.12158966064453</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1188</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1660</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1636</v>
+      </c>
+      <c r="F5" s="1">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>13.89605140686035</v>
+      </c>
+      <c r="C6" s="1">
         <v>1024</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D6" s="1">
         <v>424</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E6" s="1">
         <v>36</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F6" s="1">
         <v>388</v>
       </c>
-      <c r="G4" s="1">
-        <v>0</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>1024</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32">
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>3.691138505935669</v>
+      </c>
+      <c r="C7" s="1">
+        <v>272</v>
+      </c>
+      <c r="D7" s="1">
+        <v>546</v>
+      </c>
+      <c r="E7" s="1">
+        <v>546</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2.632650375366211</v>
+      </c>
+      <c r="C8" s="1">
+        <v>194</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2949</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2758</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>191</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2.496946573257446</v>
+      </c>
+      <c r="C9" s="1">
+        <v>184</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1126</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1126</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2.116976499557495</v>
+      </c>
+      <c r="C10" s="1">
+        <v>156</v>
+      </c>
+      <c r="D10" s="1">
+        <v>382</v>
+      </c>
+      <c r="E10" s="1">
+        <v>382</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1.737006425857544</v>
+      </c>
+      <c r="C11" s="1">
+        <v>128</v>
+      </c>
+      <c r="D11" s="1">
+        <v>64</v>
+      </c>
+      <c r="E11" s="1">
+        <v>64</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1.560591697692871</v>
+      </c>
+      <c r="C12" s="1">
+        <v>115</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1482</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1370</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>112</v>
+      </c>
+      <c r="H12" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>1.031347513198853</v>
+      </c>
+      <c r="C13" s="1">
+        <v>76</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1232</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1220</v>
+      </c>
+      <c r="F13" s="1">
+        <v>4</v>
+      </c>
+      <c r="G13" s="1">
+        <v>8</v>
+      </c>
+      <c r="H13" s="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.9906364679336548</v>
+      </c>
+      <c r="C14" s="1">
+        <v>73</v>
+      </c>
+      <c r="D14" s="1">
+        <v>6121</v>
+      </c>
+      <c r="E14" s="1">
+        <v>6078</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>43</v>
+      </c>
+      <c r="H14" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.7870810031890869</v>
+      </c>
+      <c r="C15" s="1">
+        <v>58</v>
+      </c>
+      <c r="D15" s="1">
+        <v>4730</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4730</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.3392590582370758</v>
+      </c>
+      <c r="C16" s="1">
+        <v>25</v>
+      </c>
+      <c r="D16" s="1">
+        <v>2454</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2446</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.2985479831695557</v>
+      </c>
+      <c r="C17" s="1">
+        <v>22</v>
+      </c>
+      <c r="D17" s="1">
+        <v>982</v>
+      </c>
+      <c r="E17" s="1">
+        <v>982</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.2714072465896606</v>
+      </c>
+      <c r="C18" s="1">
+        <v>20</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1360</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1360</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.2306961566209793</v>
+      </c>
+      <c r="C19" s="1">
+        <v>17</v>
+      </c>
+      <c r="D19" s="1">
+        <v>2238</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2228</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>10</v>
+      </c>
+      <c r="H19" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.2306961566209793</v>
+      </c>
+      <c r="C20" s="1">
+        <v>17</v>
+      </c>
+      <c r="D20" s="1">
+        <v>313</v>
+      </c>
+      <c r="E20" s="1">
+        <v>292</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="G20" s="1">
+        <v>16</v>
+      </c>
+      <c r="H20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.1492739915847778</v>
+      </c>
+      <c r="C21" s="1">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1">
+        <v>292</v>
+      </c>
+      <c r="E21" s="1">
+        <v>290</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2</v>
+      </c>
+      <c r="H21" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.05428145080804825</v>
+      </c>
+      <c r="C22" s="1">
+        <v>4</v>
+      </c>
+      <c r="D22" s="1">
+        <v>114</v>
+      </c>
+      <c r="E22" s="1">
+        <v>114</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.05428145080804825</v>
+      </c>
+      <c r="C23" s="1">
+        <v>4</v>
+      </c>
+      <c r="D23" s="1">
+        <v>602</v>
+      </c>
+      <c r="E23" s="1">
+        <v>582</v>
+      </c>
+      <c r="F23" s="1">
+        <v>16</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.04071108624339104</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1">
+        <v>271</v>
+      </c>
+      <c r="E24" s="1">
+        <v>270</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0.01357036270201206</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1">
+        <v>632</v>
+      </c>
+      <c r="E25" s="1">
+        <v>632</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>0.01357036270201206</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>251</v>
+      </c>
+      <c r="E26" s="1">
+        <v>250</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.01357036270201206</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1</v>
+      </c>
+      <c r="D27" s="1">
+        <v>116</v>
+      </c>
+      <c r="E27" s="1">
+        <v>116</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C32">
+      <c r="C78">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D32">
+      <c r="D78">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E32">
+      <c r="E78">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F32">
+      <c r="F78">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G32">
+      <c r="G78">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H32">
+      <c r="H78">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1064,7 +2214,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1077,71 +2227,71 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2">
-        <v>90.69330596923828</v>
+        <v>12.93178081512451</v>
       </c>
       <c r="C3" s="1">
-        <v>40539</v>
+        <v>6121</v>
       </c>
       <c r="D3" s="1">
-        <v>6298</v>
+        <v>73</v>
       </c>
       <c r="E3" s="1">
-        <v>40070</v>
+        <v>6078</v>
       </c>
       <c r="F3" s="1">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>378</v>
+        <v>43</v>
       </c>
       <c r="H3" s="1">
-        <v>5920</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>2.899393796920776</v>
+        <v>9.993027687072754</v>
       </c>
       <c r="C4" s="1">
-        <v>1296</v>
+        <v>4730</v>
       </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="E4" s="1">
-        <v>1296</v>
+        <v>4730</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1150,131 +2300,131 @@
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>1.248350024223328</v>
+        <v>6.230325698852539</v>
       </c>
       <c r="C5" s="1">
-        <v>558</v>
+        <v>2949</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="E5" s="1">
-        <v>558</v>
+        <v>2758</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H5" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2">
-        <v>0.9485670924186707</v>
+        <v>5.184543609619141</v>
       </c>
       <c r="C6" s="1">
-        <v>424</v>
+        <v>2454</v>
       </c>
       <c r="D6" s="1">
-        <v>1024</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1">
-        <v>36</v>
+        <v>2446</v>
       </c>
       <c r="F6" s="1">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H6" s="1">
-        <v>1024</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>0.7472202777862549</v>
+        <v>4.728202342987061</v>
       </c>
       <c r="C7" s="1">
-        <v>334</v>
+        <v>2238</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1">
-        <v>334</v>
+        <v>2228</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>0.5100785493850708</v>
+        <v>3.507066965103149</v>
       </c>
       <c r="C8" s="1">
-        <v>228</v>
+        <v>1660</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E8" s="1">
-        <v>228</v>
+        <v>1636</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B9" s="2">
-        <v>0.4966554045677185</v>
+        <v>3.304248571395874</v>
       </c>
       <c r="C9" s="1">
-        <v>222</v>
+        <v>1564</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>222</v>
+        <v>1524</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -1285,45 +2435,45 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>0.4161166846752167</v>
+        <v>3.13100790977478</v>
       </c>
       <c r="C10" s="1">
-        <v>186</v>
+        <v>1482</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E10" s="1">
-        <v>186</v>
+        <v>1370</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>0.2460905164480209</v>
+        <v>3.046500444412231</v>
       </c>
       <c r="C11" s="1">
-        <v>110</v>
+        <v>1442</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>110</v>
+        <v>1442</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -1337,19 +2487,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2">
-        <v>0.2192442715167999</v>
+        <v>2.873259782791138</v>
       </c>
       <c r="C12" s="1">
-        <v>98</v>
+        <v>1360</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E12" s="1">
-        <v>98</v>
+        <v>1360</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1358,24 +2508,24 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2">
-        <v>0.2192442715167999</v>
+        <v>2.759174346923828</v>
       </c>
       <c r="C13" s="1">
-        <v>98</v>
+        <v>1306</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>98</v>
+        <v>1306</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1389,19 +2539,19 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2">
-        <v>0.1923980414867401</v>
+        <v>2.738047361373901</v>
       </c>
       <c r="C14" s="1">
-        <v>86</v>
+        <v>1296</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>86</v>
+        <v>1296</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1415,45 +2565,45 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>0.1387055665254593</v>
+        <v>2.602835178375244</v>
       </c>
       <c r="C15" s="1">
-        <v>62</v>
+        <v>1232</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E15" s="1">
-        <v>62</v>
+        <v>1220</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2">
-        <v>0.1252824515104294</v>
+        <v>2.378890037536621</v>
       </c>
       <c r="C16" s="1">
-        <v>56</v>
+        <v>1126</v>
       </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>184</v>
       </c>
       <c r="E16" s="1">
-        <v>56</v>
+        <v>1126</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1462,24 +2612,24 @@
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>0.1073849499225617</v>
+        <v>2.285931587219238</v>
       </c>
       <c r="C17" s="1">
-        <v>48</v>
+        <v>1082</v>
       </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>2228</v>
       </c>
       <c r="E17" s="1">
-        <v>48</v>
+        <v>1082</v>
       </c>
       <c r="F17" s="1">
         <v>0</v>
@@ -1488,24 +2638,24 @@
         <v>0</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B18" s="2">
-        <v>0.0894874632358551</v>
+        <v>2.159170150756836</v>
       </c>
       <c r="C18" s="1">
-        <v>40</v>
+        <v>1022</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
       </c>
       <c r="E18" s="1">
-        <v>40</v>
+        <v>1022</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1519,19 +2669,19 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>0.08501308411359787</v>
+        <v>2.074662446975708</v>
       </c>
       <c r="C19" s="1">
-        <v>38</v>
+        <v>982</v>
       </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E19" s="1">
-        <v>38</v>
+        <v>982</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1540,24 +2690,24 @@
         <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B20" s="2">
-        <v>0.08053871244192123</v>
+        <v>1.926774144172669</v>
       </c>
       <c r="C20" s="1">
-        <v>36</v>
+        <v>912</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>36</v>
+        <v>912</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1571,19 +2721,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2">
-        <v>0.08053871244192123</v>
+        <v>1.694378137588501</v>
       </c>
       <c r="C21" s="1">
-        <v>36</v>
+        <v>802</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>36</v>
+        <v>802</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1597,19 +2747,19 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2">
-        <v>0.0760643407702446</v>
+        <v>1.470432877540588</v>
       </c>
       <c r="C22" s="1">
-        <v>34</v>
+        <v>696</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>34</v>
+        <v>696</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1623,19 +2773,19 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>0.07158996909856796</v>
+        <v>1.335220694541931</v>
       </c>
       <c r="C23" s="1">
-        <v>32</v>
+        <v>632</v>
       </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="1">
-        <v>32</v>
+        <v>632</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -1644,24 +2794,24 @@
         <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B24" s="2">
-        <v>0.06711559742689133</v>
+        <v>1.28874146938324</v>
       </c>
       <c r="C24" s="1">
-        <v>30</v>
+        <v>610</v>
       </c>
       <c r="D24" s="1">
-        <v>0</v>
+        <v>1547</v>
       </c>
       <c r="E24" s="1">
-        <v>30</v>
+        <v>610</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -1670,30 +2820,30 @@
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>0</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B25" s="2">
-        <v>0.06711559742689133</v>
+        <v>1.27183997631073</v>
       </c>
       <c r="C25" s="1">
-        <v>30</v>
+        <v>602</v>
       </c>
       <c r="D25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E25" s="1">
-        <v>30</v>
+        <v>582</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -1701,19 +2851,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2">
-        <v>0.06264122575521469</v>
+        <v>1.27183997631073</v>
       </c>
       <c r="C26" s="1">
-        <v>28</v>
+        <v>602</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>28</v>
+        <v>602</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -1727,19 +2877,19 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2">
-        <v>0.05816685035824776</v>
+        <v>1.178881525993347</v>
       </c>
       <c r="C27" s="1">
-        <v>26</v>
+        <v>558</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>26</v>
+        <v>558</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -1753,19 +2903,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B28" s="2">
-        <v>0.01789749227464199</v>
+        <v>1.153529286384583</v>
       </c>
       <c r="C28" s="1">
-        <v>8</v>
+        <v>546</v>
       </c>
       <c r="D28" s="1">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="E28" s="1">
-        <v>8</v>
+        <v>546</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -1774,24 +2924,24 @@
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>0</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2">
-        <v>0.01789749227464199</v>
+        <v>1.064796209335327</v>
       </c>
       <c r="C29" s="1">
-        <v>8</v>
+        <v>504</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>8</v>
+        <v>504</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -1805,85 +2955,1281 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B30" s="2">
-        <v>0.008948746137320995</v>
+        <v>0.8957809805870056</v>
       </c>
       <c r="C30" s="1">
-        <v>4</v>
+        <v>424</v>
       </c>
       <c r="D30" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E30" s="1">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2">
-        <v>0.008948746137320995</v>
+        <v>0.8408510088920593</v>
       </c>
       <c r="C31" s="1">
+        <v>398</v>
+      </c>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
+      <c r="E31" s="1">
+        <v>398</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.807047963142395</v>
+      </c>
+      <c r="C32" s="1">
+        <v>382</v>
+      </c>
+      <c r="D32" s="1">
+        <v>156</v>
+      </c>
+      <c r="E32" s="1">
+        <v>382</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
+        <v>0</v>
+      </c>
+      <c r="H32" s="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.7183149456977844</v>
+      </c>
+      <c r="C33" s="1">
+        <v>340</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>340</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
+        <v>0</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.7056387662887573</v>
+      </c>
+      <c r="C34" s="1">
+        <v>334</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>334</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.6887372732162476</v>
+      </c>
+      <c r="C35" s="1">
+        <v>326</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0</v>
+      </c>
+      <c r="E35" s="1">
+        <v>326</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>0</v>
+      </c>
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.6612722873687744</v>
+      </c>
+      <c r="C36" s="1">
+        <v>313</v>
+      </c>
+      <c r="D36" s="1">
+        <v>17</v>
+      </c>
+      <c r="E36" s="1">
+        <v>292</v>
+      </c>
+      <c r="F36" s="1">
+        <v>5</v>
+      </c>
+      <c r="G36" s="1">
+        <v>16</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.6422580480575562</v>
+      </c>
+      <c r="C37" s="1">
+        <v>304</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1">
+        <v>304</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.6169057488441467</v>
+      </c>
+      <c r="C38" s="1">
+        <v>292</v>
+      </c>
+      <c r="D38" s="1">
+        <v>11</v>
+      </c>
+      <c r="E38" s="1">
+        <v>290</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
+        <v>2</v>
+      </c>
+      <c r="H38" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.5915534496307373</v>
+      </c>
+      <c r="C39" s="1">
+        <v>280</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
+      <c r="E39" s="1">
+        <v>280</v>
+      </c>
+      <c r="F39" s="1">
+        <v>0</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.5725392699241638</v>
+      </c>
+      <c r="C40" s="1">
+        <v>271</v>
+      </c>
+      <c r="D40" s="1">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1">
+        <v>270</v>
+      </c>
+      <c r="F40" s="1">
+        <v>0</v>
+      </c>
+      <c r="G40" s="1">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.5302854180335999</v>
+      </c>
+      <c r="C41" s="1">
+        <v>251</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>250</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.5028204321861267</v>
+      </c>
+      <c r="C42" s="1">
+        <v>238</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
+        <v>238</v>
+      </c>
+      <c r="F42" s="1">
+        <v>0</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.4859189093112946</v>
+      </c>
+      <c r="C43" s="1">
+        <v>230</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
+      <c r="E43" s="1">
+        <v>230</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0</v>
+      </c>
+      <c r="G43" s="1">
+        <v>0</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0.4816935360431671</v>
+      </c>
+      <c r="C44" s="1">
+        <v>228</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>228</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.4690173864364624</v>
+      </c>
+      <c r="C45" s="1">
+        <v>222</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
+      <c r="E45" s="1">
+        <v>222</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="2">
+        <v>0.4183128178119659</v>
+      </c>
+      <c r="C46" s="1">
+        <v>198</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
+      <c r="E46" s="1">
+        <v>198</v>
+      </c>
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
+        <v>0</v>
+      </c>
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B47" s="2">
+        <v>0.3929605185985565</v>
+      </c>
+      <c r="C47" s="1">
+        <v>186</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1">
+        <v>186</v>
+      </c>
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
+        <v>0</v>
+      </c>
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.2831005752086639</v>
+      </c>
+      <c r="C48" s="1">
+        <v>134</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
+      <c r="E48" s="1">
+        <v>134</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>0</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.2492975294589996</v>
+      </c>
+      <c r="C49" s="1">
+        <v>118</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
+      <c r="E49" s="1">
+        <v>118</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0</v>
+      </c>
+      <c r="G49" s="1">
+        <v>0</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0.245072141289711</v>
+      </c>
+      <c r="C50" s="1">
+        <v>116</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1</v>
+      </c>
+      <c r="E50" s="1">
+        <v>116</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0.2408467680215836</v>
+      </c>
+      <c r="C51" s="1">
+        <v>114</v>
+      </c>
+      <c r="D51" s="1">
         <v>4</v>
       </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="E51" s="1">
+        <v>114</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0</v>
+      </c>
+      <c r="G51" s="1">
+        <v>0</v>
+      </c>
+      <c r="H51" s="1">
         <v>4</v>
       </c>
-      <c r="F31" s="1">
-        <v>0</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32">
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>0.2323960065841675</v>
+      </c>
+      <c r="C52" s="1">
+        <v>110</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1">
+        <v>110</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0</v>
+      </c>
+      <c r="G52" s="1">
+        <v>0</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0.2070437073707581</v>
+      </c>
+      <c r="C53" s="1">
+        <v>98</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0</v>
+      </c>
+      <c r="E53" s="1">
+        <v>98</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0.2070437073707581</v>
+      </c>
+      <c r="C54" s="1">
+        <v>98</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0</v>
+      </c>
+      <c r="E54" s="1">
+        <v>98</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0</v>
+      </c>
+      <c r="G54" s="1">
+        <v>0</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0.1816914230585098</v>
+      </c>
+      <c r="C55" s="1">
+        <v>86</v>
+      </c>
+      <c r="D55" s="1">
+        <v>0</v>
+      </c>
+      <c r="E55" s="1">
+        <v>86</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0</v>
+      </c>
+      <c r="G55" s="1">
+        <v>0</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="2">
+        <v>0.1352122128009796</v>
+      </c>
+      <c r="C56" s="1">
+        <v>64</v>
+      </c>
+      <c r="D56" s="1">
+        <v>128</v>
+      </c>
+      <c r="E56" s="1">
+        <v>64</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0</v>
+      </c>
+      <c r="G56" s="1">
+        <v>0</v>
+      </c>
+      <c r="H56" s="1">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="2">
+        <v>0.1309868395328522</v>
+      </c>
+      <c r="C57" s="1">
+        <v>62</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0</v>
+      </c>
+      <c r="E57" s="1">
+        <v>62</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0</v>
+      </c>
+      <c r="G57" s="1">
+        <v>0</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="2">
+        <v>0.1183106899261475</v>
+      </c>
+      <c r="C58" s="1">
+        <v>56</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0</v>
+      </c>
+      <c r="E58" s="1">
+        <v>56</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0</v>
+      </c>
+      <c r="G58" s="1">
+        <v>0</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="2">
+        <v>0.1098599284887314</v>
+      </c>
+      <c r="C59" s="1">
+        <v>52</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1">
+        <v>52</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0</v>
+      </c>
+      <c r="G59" s="1">
+        <v>0</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0.1056345477700234</v>
+      </c>
+      <c r="C60" s="1">
+        <v>50</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0</v>
+      </c>
+      <c r="E60" s="1">
+        <v>50</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0</v>
+      </c>
+      <c r="G60" s="1">
+        <v>0</v>
+      </c>
+      <c r="H60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0.1014091670513153</v>
+      </c>
+      <c r="C61" s="1">
+        <v>48</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0</v>
+      </c>
+      <c r="E61" s="1">
+        <v>48</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0</v>
+      </c>
+      <c r="G61" s="1">
+        <v>0</v>
+      </c>
+      <c r="H61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" s="2">
+        <v>0.08450763672590256</v>
+      </c>
+      <c r="C62" s="1">
+        <v>40</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0</v>
+      </c>
+      <c r="E62" s="1">
+        <v>40</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>0</v>
+      </c>
+      <c r="H62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="2">
+        <v>0.08028225600719452</v>
+      </c>
+      <c r="C63" s="1">
+        <v>38</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0</v>
+      </c>
+      <c r="E63" s="1">
+        <v>38</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="2">
+        <v>0.07605687528848648</v>
+      </c>
+      <c r="C64" s="1">
+        <v>36</v>
+      </c>
+      <c r="D64" s="1">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1">
+        <v>36</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" s="2">
+        <v>0.07605687528848648</v>
+      </c>
+      <c r="C65" s="1">
+        <v>36</v>
+      </c>
+      <c r="D65" s="1">
+        <v>0</v>
+      </c>
+      <c r="E65" s="1">
+        <v>36</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.07183149456977844</v>
+      </c>
+      <c r="C66" s="1">
+        <v>34</v>
+      </c>
+      <c r="D66" s="1">
+        <v>0</v>
+      </c>
+      <c r="E66" s="1">
+        <v>34</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.06760610640048981</v>
+      </c>
+      <c r="C67" s="1">
+        <v>32</v>
+      </c>
+      <c r="D67" s="1">
+        <v>0</v>
+      </c>
+      <c r="E67" s="1">
+        <v>32</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.06338072568178177</v>
+      </c>
+      <c r="C68" s="1">
+        <v>30</v>
+      </c>
+      <c r="D68" s="1">
+        <v>0</v>
+      </c>
+      <c r="E68" s="1">
+        <v>30</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.06338072568178177</v>
+      </c>
+      <c r="C69" s="1">
+        <v>30</v>
+      </c>
+      <c r="D69" s="1">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1">
+        <v>30</v>
+      </c>
+      <c r="F69" s="1">
+        <v>0</v>
+      </c>
+      <c r="G69" s="1">
+        <v>0</v>
+      </c>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.05915534496307373</v>
+      </c>
+      <c r="C70" s="1">
+        <v>28</v>
+      </c>
+      <c r="D70" s="1">
+        <v>0</v>
+      </c>
+      <c r="E70" s="1">
+        <v>28</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0</v>
+      </c>
+      <c r="G70" s="1">
+        <v>0</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.05915534496307373</v>
+      </c>
+      <c r="C71" s="1">
+        <v>28</v>
+      </c>
+      <c r="D71" s="1">
+        <v>0</v>
+      </c>
+      <c r="E71" s="1">
+        <v>28</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0</v>
+      </c>
+      <c r="G71" s="1">
+        <v>0</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="2">
+        <v>0.05492996424436569</v>
+      </c>
+      <c r="C72" s="1">
+        <v>26</v>
+      </c>
+      <c r="D72" s="1">
+        <v>0</v>
+      </c>
+      <c r="E72" s="1">
+        <v>26</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0</v>
+      </c>
+      <c r="G72" s="1">
+        <v>0</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.03802843764424324</v>
+      </c>
+      <c r="C73" s="1">
+        <v>18</v>
+      </c>
+      <c r="D73" s="1">
+        <v>0</v>
+      </c>
+      <c r="E73" s="1">
+        <v>18</v>
+      </c>
+      <c r="F73" s="1">
+        <v>0</v>
+      </c>
+      <c r="G73" s="1">
+        <v>0</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" s="2">
+        <v>0.01690152660012245</v>
+      </c>
+      <c r="C74" s="1">
+        <v>8</v>
+      </c>
+      <c r="D74" s="1">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1">
+        <v>8</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0</v>
+      </c>
+      <c r="G74" s="1">
+        <v>0</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" s="2">
+        <v>0.01690152660012245</v>
+      </c>
+      <c r="C75" s="1">
+        <v>8</v>
+      </c>
+      <c r="D75" s="1">
+        <v>0</v>
+      </c>
+      <c r="E75" s="1">
+        <v>8</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0</v>
+      </c>
+      <c r="G75" s="1">
+        <v>0</v>
+      </c>
+      <c r="H75" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" s="2">
+        <v>0.008450763300061226</v>
+      </c>
+      <c r="C76" s="1">
+        <v>4</v>
+      </c>
+      <c r="D76" s="1">
+        <v>0</v>
+      </c>
+      <c r="E76" s="1">
+        <v>4</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0</v>
+      </c>
+      <c r="G76" s="1">
+        <v>0</v>
+      </c>
+      <c r="H76" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="2">
+        <v>0.008450763300061226</v>
+      </c>
+      <c r="C77" s="1">
+        <v>4</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <v>4</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C32">
+      <c r="C78">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D32">
+      <c r="D78">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E32">
+      <c r="E78">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F32">
+      <c r="F78">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G32">
+      <c r="G78">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H32">
+      <c r="H78">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/app/project/MDK_V5/AT32F403ARGT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F403ARGT7_WorkBench_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="88">
   <si>
     <t>AT32F403ARGT7_WorkBench</t>
   </si>
@@ -116,6 +116,9 @@
     <t>at32f403a_407_usart.o</t>
   </si>
   <si>
+    <t>at32f403a_407_dma.o</t>
+  </si>
+  <si>
     <t>at32f403a_407_wk_config.o</t>
   </si>
   <si>
@@ -125,6 +128,9 @@
     <t>mc_w.l</t>
   </si>
   <si>
+    <t>wk_adc.o</t>
+  </si>
+  <si>
     <t>at32f403a_407_misc.o</t>
   </si>
   <si>
@@ -137,9 +143,6 @@
     <t>dadd.o</t>
   </si>
   <si>
-    <t>wk_adc.o</t>
-  </si>
-  <si>
     <t>wk_tmr.o</t>
   </si>
   <si>
@@ -165,6 +168,9 @@
   </si>
   <si>
     <t>wk_dac.o</t>
+  </si>
+  <si>
+    <t>wk_dma.o</t>
   </si>
   <si>
     <t>at32f403a_407_wdt.o</t>
@@ -362,9 +368,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$78</c:f>
+              <c:f>ram_percent!$A$3:$A$80</c:f>
               <c:strCache>
-                <c:ptCount val="76"/>
+                <c:ptCount val="78"/>
                 <c:pt idx="0">
                   <c:v>at32_usart.o</c:v>
                 </c:pt>
@@ -440,7 +446,7 @@
                 <c:pt idx="24">
                   <c:v>iap.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="77">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -448,86 +454,86 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$78</c:f>
+              <c:f>ram_percent!$B$3:$B$80</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="78"/>
                 <c:pt idx="0">
-                  <c:v>30.23476791381836</c:v>
+                  <c:v>30.05125427246094</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.99335098266602</c:v>
+                  <c:v>20.86592864990234</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16.12158966064453</c:v>
+                  <c:v>16.02373886108398</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>13.89605140686035</c:v>
+                  <c:v>13.81170749664307</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.691138505935669</c:v>
+                  <c:v>4.316158771514893</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.632650375366211</c:v>
+                  <c:v>2.616671085357666</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.496946573257446</c:v>
+                  <c:v>2.481791257858276</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.116976499557495</c:v>
+                  <c:v>2.104127407073975</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.737006425857544</c:v>
+                  <c:v>1.726463437080383</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.560591697692871</c:v>
+                  <c:v>1.551119446754456</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.031347513198853</c:v>
+                  <c:v>1.025087714195252</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.9906364679336548</c:v>
+                  <c:v>0.9441596865653992</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.7870810031890869</c:v>
+                  <c:v>0.7823037505149841</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.3392590582370758</c:v>
+                  <c:v>0.3371998965740204</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.2985479831695557</c:v>
+                  <c:v>0.2967359125614166</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.2714072465896606</c:v>
+                  <c:v>0.2697599232196808</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.2306961566209793</c:v>
+                  <c:v>0.2292959243059158</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.2306961566209793</c:v>
+                  <c:v>0.2292959243059158</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.1492739915847778</c:v>
+                  <c:v>0.1483679562807083</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.05428145080804825</c:v>
+                  <c:v>0.05395198240876198</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.05428145080804825</c:v>
+                  <c:v>0.05395198240876198</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.04071108624339104</c:v>
+                  <c:v>0.04046398773789406</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.01357036270201206</c:v>
+                  <c:v>0.0134879956021905</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.01357036270201206</c:v>
+                  <c:v>0.0134879956021905</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.01357036270201206</c:v>
-                </c:pt>
-                <c:pt idx="75">
+                  <c:v>0.0134879956021905</c:v>
+                </c:pt>
+                <c:pt idx="77">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -595,9 +601,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$78</c:f>
+              <c:f>flash_percent!$A$3:$A$80</c:f>
               <c:strCache>
-                <c:ptCount val="76"/>
+                <c:ptCount val="78"/>
                 <c:pt idx="0">
                   <c:v>lcd_handle.o</c:v>
                 </c:pt>
@@ -626,13 +632,13 @@
                   <c:v>at32f403a_407_flash.o</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>at32f403a_407_tmr.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>mf_w.l</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>collect_data_handle.o</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>at32f403a_407_tmr.o</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>mf_w.l</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>perf_counter.o</c:v>
@@ -653,177 +659,183 @@
                   <c:v>at32f403a_407_adc.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
+                  <c:v>adc_filter.o</c:v>
+                </c:pt>
+                <c:pt idx="19">
                   <c:v>at32f403a_407_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>at32f403a_407_wk_config.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
+                  <c:v>at32f403a_407_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>at32f403a_407_wk_config.o</c:v>
+                </c:pt>
+                <c:pt idx="23">
                   <c:v>pc_comm_handle.o</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>system_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
                   <c:v>at32f403a_407_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>mc_w.l</c:v>
                 </c:pt>
-                <c:pt idx="25">
-                  <c:v>adc_filter.o</c:v>
-                </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
+                  <c:v>wk_adc.o</c:v>
+                </c:pt>
+                <c:pt idx="28">
                   <c:v>at32f403a_407_misc.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>startup_at32f403a_407.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>wk_gpio.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>ps305d_handle.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>at32f403a_407_dac.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>dadd.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
-                  <c:v>wk_adc.o</c:v>
-                </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="34">
                   <c:v>beep.o</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="35">
                   <c:v>wk_tmr.o</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="36">
                   <c:v>at32f403a_407_int.o</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="37">
                   <c:v>util_queue.o</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="38">
                   <c:v>beep_handle.o</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="39">
                   <c:v>key.o</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="40">
                   <c:v>at32f403a_407_crc.o</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="41">
                   <c:v>perfc_port_default.o</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="42">
                   <c:v>dmul.o</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="43">
                   <c:v>ddiv.o</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="44">
                   <c:v>wk_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="45">
                   <c:v>depilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="46">
                   <c:v>wk_dac.o</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="47">
+                  <c:v>wk_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="48">
                   <c:v>at32f403a_407_wdt.o</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="49">
                   <c:v>iap.o</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="50">
                   <c:v>wk_system.o</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="51">
                   <c:v>fepilogue.o</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="52">
                   <c:v>uldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="53">
                   <c:v>ldiv.o</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="54">
                   <c:v>__dczerorl2.o</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="55">
                   <c:v>pid_handle.o</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="56">
                   <c:v>dfixi.o</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="57">
                   <c:v>d2f.o</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="58">
                   <c:v>wk_crc.o</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="59">
                   <c:v>flash.o</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="60">
                   <c:v>init.o</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="61">
                   <c:v>cpp_init.o</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="62">
                   <c:v>f2d.o</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="63">
                   <c:v>memseta.o</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="64">
                   <c:v>llsshr.o</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="65">
                   <c:v>dflti.o</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="66">
                   <c:v>llushr.o</c:v>
                 </c:pt>
-                <c:pt idx="65">
+                <c:pt idx="67">
                   <c:v>llshl.o</c:v>
                 </c:pt>
-                <c:pt idx="66">
+                <c:pt idx="68">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="67">
+                <c:pt idx="69">
                   <c:v>wk_wdt.o</c:v>
                 </c:pt>
-                <c:pt idx="68">
+                <c:pt idx="70">
                   <c:v>systick_wrapper_gnu.o</c:v>
                 </c:pt>
-                <c:pt idx="69">
+                <c:pt idx="71">
                   <c:v>dfltui.o</c:v>
                 </c:pt>
-                <c:pt idx="70">
+                <c:pt idx="72">
                   <c:v>wk_debug.o</c:v>
                 </c:pt>
-                <c:pt idx="71">
+                <c:pt idx="73">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="72">
+                <c:pt idx="74">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="73">
+                <c:pt idx="75">
                   <c:v>entry8a.o</c:v>
                 </c:pt>
-                <c:pt idx="74">
+                <c:pt idx="76">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="75">
+                <c:pt idx="77">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -831,236 +843,242 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$78</c:f>
+              <c:f>flash_percent!$B$3:$B$80</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="76"/>
+                <c:ptCount val="78"/>
                 <c:pt idx="0">
-                  <c:v>12.93178081512451</c:v>
+                  <c:v>11.63311386108398</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.993027687072754</c:v>
+                  <c:v>9.806564331054688</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.230325698852539</c:v>
+                  <c:v>6.114071369171143</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.184543609619141</c:v>
+                  <c:v>5.067070484161377</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.728202342987061</c:v>
+                  <c:v>4.639976978302002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.507066965103149</c:v>
+                  <c:v>3.441627025604248</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.304248571395874</c:v>
+                  <c:v>3.242593288421631</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.13100790977478</c:v>
+                  <c:v>3.072585105895996</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.046500444412231</c:v>
+                  <c:v>2.989654302597046</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.873259782791138</c:v>
+                  <c:v>2.707689762115479</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.759174346923828</c:v>
+                  <c:v>2.686957120895386</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.738047361373901</c:v>
+                  <c:v>2.595733165740967</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.602835178375244</c:v>
+                  <c:v>2.554267883300781</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.378890037536621</c:v>
+                  <c:v>2.334501266479492</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.285931587219238</c:v>
+                  <c:v>2.243277311325073</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.159170150756836</c:v>
+                  <c:v>2.118881225585938</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.074662446975708</c:v>
+                  <c:v>2.035950422286987</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.926774144172669</c:v>
+                  <c:v>1.961312770843506</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.694378137588501</c:v>
+                  <c:v>1.870088934898377</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.470432877540588</c:v>
+                  <c:v>1.662762045860291</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.335220694541931</c:v>
+                  <c:v>1.525926232337952</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.28874146938324</c:v>
+                  <c:v>1.501047015190125</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.27183997631073</c:v>
+                  <c:v>1.488607406616211</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.27183997631073</c:v>
+                  <c:v>1.264694333076477</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.178881525993347</c:v>
+                  <c:v>1.248108148574829</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.153529286384583</c:v>
+                  <c:v>1.248108148574829</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.064796209335327</c:v>
+                  <c:v>1.1568843126297</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.8957809805870056</c:v>
+                  <c:v>1.078100085258484</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.8408510088920593</c:v>
+                  <c:v>1.044927716255188</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.807047963142395</c:v>
+                  <c:v>0.8790662288665772</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.7183149456977844</c:v>
+                  <c:v>0.8251612186431885</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.7056387662887573</c:v>
+                  <c:v>0.7339373230934143</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.6887372732162476</c:v>
+                  <c:v>0.7049115896224976</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.6612722873687744</c:v>
+                  <c:v>0.692471981048584</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.6422580480575562</c:v>
+                  <c:v>0.6489332914352417</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.6169057488441467</c:v>
+                  <c:v>0.6302738785743713</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.5915534496307373</c:v>
+                  <c:v>0.6053946614265442</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.5725392699241638</c:v>
+                  <c:v>0.580515444278717</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.5302854180335999</c:v>
+                  <c:v>0.5618559718132019</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.5028204321861267</c:v>
+                  <c:v>0.5203906297683716</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.4859189093112946</c:v>
+                  <c:v>0.4934380948543549</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.4816935360431671</c:v>
+                  <c:v>0.4768519401550293</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.4690173864364624</c:v>
+                  <c:v>0.4727054238319397</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.4183128178119659</c:v>
+                  <c:v>0.4602657854557037</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.3929605185985565</c:v>
+                  <c:v>0.4105073213577271</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.2831005752086639</c:v>
+                  <c:v>0.3856281042098999</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2492975294589996</c:v>
+                  <c:v>0.2778180837631226</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.245072141289711</c:v>
+                  <c:v>0.2529388666152954</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.2408467680215836</c:v>
+                  <c:v>0.2446457892656326</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.2323960065841675</c:v>
+                  <c:v>0.2404992431402206</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.2070437073707581</c:v>
+                  <c:v>0.2363527119159699</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.2070437073707581</c:v>
+                  <c:v>0.2280596345663071</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.1816914230585098</c:v>
+                  <c:v>0.2031804025173187</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.1352122128009796</c:v>
+                  <c:v>0.2031804025173187</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1309868395328522</c:v>
+                  <c:v>0.1783011704683304</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1183106899261475</c:v>
+                  <c:v>0.1326892375946045</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1098599284887314</c:v>
+                  <c:v>0.1285427063703537</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1056345477700234</c:v>
+                  <c:v>0.1161030828952789</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1014091670513153</c:v>
+                  <c:v>0.1078100055456162</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.08450763672590256</c:v>
+                  <c:v>0.1036634668707848</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.08028225600719452</c:v>
+                  <c:v>0.09951692819595337</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.07605687528848648</c:v>
+                  <c:v>0.08293077349662781</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.07605687528848648</c:v>
+                  <c:v>0.07878423482179642</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.07183149456977844</c:v>
+                  <c:v>0.07463769614696503</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.06760610640048981</c:v>
+                  <c:v>0.07463769614696503</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.06338072568178177</c:v>
+                  <c:v>0.07049115747213364</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.06338072568178177</c:v>
+                  <c:v>0.06634461879730225</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.05915534496307373</c:v>
+                  <c:v>0.06219808012247086</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.05915534496307373</c:v>
+                  <c:v>0.06219808012247086</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.05492996424436569</c:v>
+                  <c:v>0.05805154144763947</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.03802843764424324</c:v>
+                  <c:v>0.05805154144763947</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.01690152660012245</c:v>
+                  <c:v>0.05390500277280808</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.01690152660012245</c:v>
+                  <c:v>0.03731884807348251</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.008450763300061226</c:v>
+                  <c:v>0.01658615469932556</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.008450763300061226</c:v>
+                  <c:v>0.01658615469932556</c:v>
                 </c:pt>
                 <c:pt idx="75">
+                  <c:v>0.008293077349662781</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.008293077349662781</c:v>
+                </c:pt>
+                <c:pt idx="77">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1165,8 +1183,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H78" totalsRowCount="1">
-  <autoFilter ref="A2:H77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H80" totalsRowCount="1">
+  <autoFilter ref="A2:H79"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -1182,8 +1200,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H78" totalsRowCount="1">
-  <autoFilter ref="A2:H77"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H80" totalsRowCount="1">
+  <autoFilter ref="A2:H79"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1483,7 +1501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1496,28 +1514,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1525,7 +1543,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>30.23476791381836</v>
+        <v>30.05125427246094</v>
       </c>
       <c r="C3" s="1">
         <v>2228</v>
@@ -1551,7 +1569,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>20.99335098266602</v>
+        <v>20.86592864990234</v>
       </c>
       <c r="C4" s="1">
         <v>1547</v>
@@ -1577,7 +1595,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>16.12158966064453</v>
+        <v>16.02373886108398</v>
       </c>
       <c r="C5" s="1">
         <v>1188</v>
@@ -1603,7 +1621,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>13.89605140686035</v>
+        <v>13.81170749664307</v>
       </c>
       <c r="C6" s="1">
         <v>1024</v>
@@ -1629,16 +1647,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>3.691138505935669</v>
+        <v>4.316158771514893</v>
       </c>
       <c r="C7" s="1">
-        <v>272</v>
+        <v>320</v>
       </c>
       <c r="D7" s="1">
-        <v>546</v>
+        <v>902</v>
       </c>
       <c r="E7" s="1">
-        <v>546</v>
+        <v>902</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
@@ -1647,7 +1665,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>272</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1655,7 +1673,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>2.632650375366211</v>
+        <v>2.616671085357666</v>
       </c>
       <c r="C8" s="1">
         <v>194</v>
@@ -1681,7 +1699,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>2.496946573257446</v>
+        <v>2.481791257858276</v>
       </c>
       <c r="C9" s="1">
         <v>184</v>
@@ -1707,16 +1725,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>2.116976499557495</v>
+        <v>2.104127407073975</v>
       </c>
       <c r="C10" s="1">
         <v>156</v>
       </c>
       <c r="D10" s="1">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="E10" s="1">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1733,7 +1751,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>1.737006425857544</v>
+        <v>1.726463437080383</v>
       </c>
       <c r="C11" s="1">
         <v>128</v>
@@ -1759,7 +1777,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>1.560591697692871</v>
+        <v>1.551119446754456</v>
       </c>
       <c r="C12" s="1">
         <v>115</v>
@@ -1785,7 +1803,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>1.031347513198853</v>
+        <v>1.025087714195252</v>
       </c>
       <c r="C13" s="1">
         <v>76</v>
@@ -1811,16 +1829,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.9906364679336548</v>
+        <v>0.9441596865653992</v>
       </c>
       <c r="C14" s="1">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D14" s="1">
-        <v>6121</v>
+        <v>5611</v>
       </c>
       <c r="E14" s="1">
-        <v>6078</v>
+        <v>5568</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1829,7 +1847,7 @@
         <v>43</v>
       </c>
       <c r="H14" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1837,7 +1855,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>0.7870810031890869</v>
+        <v>0.7823037505149841</v>
       </c>
       <c r="C15" s="1">
         <v>58</v>
@@ -1863,16 +1881,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
-        <v>0.3392590582370758</v>
+        <v>0.3371998965740204</v>
       </c>
       <c r="C16" s="1">
         <v>25</v>
       </c>
       <c r="D16" s="1">
-        <v>2454</v>
+        <v>2444</v>
       </c>
       <c r="E16" s="1">
-        <v>2446</v>
+        <v>2436</v>
       </c>
       <c r="F16" s="1">
         <v>0</v>
@@ -1889,7 +1907,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
-        <v>0.2985479831695557</v>
+        <v>0.2967359125614166</v>
       </c>
       <c r="C17" s="1">
         <v>22</v>
@@ -1915,16 +1933,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="2">
-        <v>0.2714072465896606</v>
+        <v>0.2697599232196808</v>
       </c>
       <c r="C18" s="1">
         <v>20</v>
       </c>
       <c r="D18" s="1">
-        <v>1360</v>
+        <v>1252</v>
       </c>
       <c r="E18" s="1">
-        <v>1360</v>
+        <v>1252</v>
       </c>
       <c r="F18" s="1">
         <v>0</v>
@@ -1941,7 +1959,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="2">
-        <v>0.2306961566209793</v>
+        <v>0.2292959243059158</v>
       </c>
       <c r="C19" s="1">
         <v>17</v>
@@ -1967,7 +1985,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="2">
-        <v>0.2306961566209793</v>
+        <v>0.2292959243059158</v>
       </c>
       <c r="C20" s="1">
         <v>17</v>
@@ -1993,7 +2011,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="2">
-        <v>0.1492739915847778</v>
+        <v>0.1483679562807083</v>
       </c>
       <c r="C21" s="1">
         <v>11</v>
@@ -2019,7 +2037,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="2">
-        <v>0.05428145080804825</v>
+        <v>0.05395198240876198</v>
       </c>
       <c r="C22" s="1">
         <v>4</v>
@@ -2045,7 +2063,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="2">
-        <v>0.05428145080804825</v>
+        <v>0.05395198240876198</v>
       </c>
       <c r="C23" s="1">
         <v>4</v>
@@ -2071,7 +2089,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="2">
-        <v>0.04071108624339104</v>
+        <v>0.04046398773789406</v>
       </c>
       <c r="C24" s="1">
         <v>3</v>
@@ -2097,16 +2115,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="2">
-        <v>0.01357036270201206</v>
+        <v>0.0134879956021905</v>
       </c>
       <c r="C25" s="1">
         <v>1</v>
       </c>
       <c r="D25" s="1">
-        <v>632</v>
+        <v>736</v>
       </c>
       <c r="E25" s="1">
-        <v>632</v>
+        <v>736</v>
       </c>
       <c r="F25" s="1">
         <v>0</v>
@@ -2123,7 +2141,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="2">
-        <v>0.01357036270201206</v>
+        <v>0.0134879956021905</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
@@ -2149,7 +2167,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2">
-        <v>0.01357036270201206</v>
+        <v>0.0134879956021905</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
@@ -2170,35 +2188,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
-        <v>77</v>
-      </c>
-      <c r="B78">
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C78">
+      <c r="C80">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D78">
+      <c r="D80">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E78">
+      <c r="E80">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F78">
+      <c r="F80">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G78">
+      <c r="G80">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H78">
+      <c r="H80">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -2214,7 +2232,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -2227,28 +2245,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" t="s">
         <v>85</v>
       </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G2" t="s">
-        <v>83</v>
-      </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -2256,16 +2274,16 @@
         <v>12</v>
       </c>
       <c r="B3" s="2">
-        <v>12.93178081512451</v>
+        <v>11.63311386108398</v>
       </c>
       <c r="C3" s="1">
-        <v>6121</v>
+        <v>5611</v>
       </c>
       <c r="D3" s="1">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E3" s="1">
-        <v>6078</v>
+        <v>5568</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -2274,7 +2292,7 @@
         <v>43</v>
       </c>
       <c r="H3" s="1">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -2282,7 +2300,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>9.993027687072754</v>
+        <v>9.806564331054688</v>
       </c>
       <c r="C4" s="1">
         <v>4730</v>
@@ -2308,7 +2326,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>6.230325698852539</v>
+        <v>6.114071369171143</v>
       </c>
       <c r="C5" s="1">
         <v>2949</v>
@@ -2334,16 +2352,16 @@
         <v>14</v>
       </c>
       <c r="B6" s="2">
-        <v>5.184543609619141</v>
+        <v>5.067070484161377</v>
       </c>
       <c r="C6" s="1">
-        <v>2454</v>
+        <v>2444</v>
       </c>
       <c r="D6" s="1">
         <v>25</v>
       </c>
       <c r="E6" s="1">
-        <v>2446</v>
+        <v>2436</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -2360,7 +2378,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>4.728202342987061</v>
+        <v>4.639976978302002</v>
       </c>
       <c r="C7" s="1">
         <v>2238</v>
@@ -2386,7 +2404,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>3.507066965103149</v>
+        <v>3.441627025604248</v>
       </c>
       <c r="C8" s="1">
         <v>1660</v>
@@ -2412,7 +2430,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="2">
-        <v>3.304248571395874</v>
+        <v>3.242593288421631</v>
       </c>
       <c r="C9" s="1">
         <v>1564</v>
@@ -2438,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>3.13100790977478</v>
+        <v>3.072585105895996</v>
       </c>
       <c r="C10" s="1">
         <v>1482</v>
@@ -2464,7 +2482,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>3.046500444412231</v>
+        <v>2.989654302597046</v>
       </c>
       <c r="C11" s="1">
         <v>1442</v>
@@ -2487,19 +2505,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>2.873259782791138</v>
+        <v>2.707689762115479</v>
       </c>
       <c r="C12" s="1">
-        <v>1360</v>
+        <v>1306</v>
       </c>
       <c r="D12" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>1360</v>
+        <v>1306</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -2508,24 +2526,24 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>2.759174346923828</v>
+        <v>2.686957120895386</v>
       </c>
       <c r="C13" s="1">
-        <v>1306</v>
+        <v>1296</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>1306</v>
+        <v>1296</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -2539,19 +2557,19 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>2.738047361373901</v>
+        <v>2.595733165740967</v>
       </c>
       <c r="C14" s="1">
-        <v>1296</v>
+        <v>1252</v>
       </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E14" s="1">
-        <v>1296</v>
+        <v>1252</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2560,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -2568,7 +2586,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>2.602835178375244</v>
+        <v>2.554267883300781</v>
       </c>
       <c r="C15" s="1">
         <v>1232</v>
@@ -2594,7 +2612,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="2">
-        <v>2.378890037536621</v>
+        <v>2.334501266479492</v>
       </c>
       <c r="C16" s="1">
         <v>1126</v>
@@ -2620,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>2.285931587219238</v>
+        <v>2.243277311325073</v>
       </c>
       <c r="C17" s="1">
         <v>1082</v>
@@ -2646,7 +2664,7 @@
         <v>30</v>
       </c>
       <c r="B18" s="2">
-        <v>2.159170150756836</v>
+        <v>2.118881225585938</v>
       </c>
       <c r="C18" s="1">
         <v>1022</v>
@@ -2672,7 +2690,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>2.074662446975708</v>
+        <v>2.035950422286987</v>
       </c>
       <c r="C19" s="1">
         <v>982</v>
@@ -2698,16 +2716,16 @@
         <v>31</v>
       </c>
       <c r="B20" s="2">
-        <v>1.926774144172669</v>
+        <v>1.961312770843506</v>
       </c>
       <c r="C20" s="1">
-        <v>912</v>
+        <v>946</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>912</v>
+        <v>946</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2721,19 +2739,19 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B21" s="2">
-        <v>1.694378137588501</v>
+        <v>1.870088934898377</v>
       </c>
       <c r="C21" s="1">
-        <v>802</v>
+        <v>902</v>
       </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="E21" s="1">
-        <v>802</v>
+        <v>902</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -2742,24 +2760,24 @@
         <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="2">
-        <v>1.470432877540588</v>
+        <v>1.662762045860291</v>
       </c>
       <c r="C22" s="1">
-        <v>696</v>
+        <v>802</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>696</v>
+        <v>802</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -2776,16 +2794,16 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>1.335220694541931</v>
+        <v>1.525926232337952</v>
       </c>
       <c r="C23" s="1">
-        <v>632</v>
+        <v>736</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
       </c>
       <c r="E23" s="1">
-        <v>632</v>
+        <v>736</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -2799,19 +2817,19 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2">
-        <v>1.28874146938324</v>
+        <v>1.501047015190125</v>
       </c>
       <c r="C24" s="1">
-        <v>610</v>
+        <v>724</v>
       </c>
       <c r="D24" s="1">
-        <v>1547</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>610</v>
+        <v>724</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2820,30 +2838,30 @@
         <v>0</v>
       </c>
       <c r="H24" s="1">
-        <v>1547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2">
-        <v>1.27183997631073</v>
+        <v>1.488607406616211</v>
       </c>
       <c r="C25" s="1">
-        <v>602</v>
+        <v>718</v>
       </c>
       <c r="D25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E25" s="1">
-        <v>582</v>
+        <v>718</v>
       </c>
       <c r="F25" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -2851,19 +2869,19 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="B26" s="2">
-        <v>1.27183997631073</v>
+        <v>1.264694333076477</v>
       </c>
       <c r="C26" s="1">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="D26" s="1">
-        <v>0</v>
+        <v>1547</v>
       </c>
       <c r="E26" s="1">
-        <v>602</v>
+        <v>610</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2872,30 +2890,30 @@
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>0</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B27" s="2">
-        <v>1.178881525993347</v>
+        <v>1.248108148574829</v>
       </c>
       <c r="C27" s="1">
-        <v>558</v>
+        <v>602</v>
       </c>
       <c r="D27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E27" s="1">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G27" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -2903,19 +2921,19 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2">
-        <v>1.153529286384583</v>
+        <v>1.248108148574829</v>
       </c>
       <c r="C28" s="1">
-        <v>546</v>
+        <v>602</v>
       </c>
       <c r="D28" s="1">
-        <v>272</v>
+        <v>0</v>
       </c>
       <c r="E28" s="1">
-        <v>546</v>
+        <v>602</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2924,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="1">
-        <v>272</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -2932,16 +2950,16 @@
         <v>36</v>
       </c>
       <c r="B29" s="2">
-        <v>1.064796209335327</v>
+        <v>1.1568843126297</v>
       </c>
       <c r="C29" s="1">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>504</v>
+        <v>558</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2955,45 +2973,45 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2">
-        <v>0.8957809805870056</v>
+        <v>1.078100085258484</v>
       </c>
       <c r="C30" s="1">
-        <v>424</v>
+        <v>520</v>
       </c>
       <c r="D30" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>36</v>
+        <v>520</v>
       </c>
       <c r="F30" s="1">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
         <v>0</v>
       </c>
       <c r="H30" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2">
-        <v>0.8408510088920593</v>
+        <v>1.044927716255188</v>
       </c>
       <c r="C31" s="1">
-        <v>398</v>
+        <v>504</v>
       </c>
       <c r="D31" s="1">
         <v>0</v>
       </c>
       <c r="E31" s="1">
-        <v>398</v>
+        <v>504</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -3007,45 +3025,45 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>0.807047963142395</v>
+        <v>0.8790662288665772</v>
       </c>
       <c r="C32" s="1">
-        <v>382</v>
+        <v>424</v>
       </c>
       <c r="D32" s="1">
-        <v>156</v>
+        <v>1024</v>
       </c>
       <c r="E32" s="1">
-        <v>382</v>
+        <v>36</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
       <c r="H32" s="1">
-        <v>156</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="2">
-        <v>0.7183149456977844</v>
+        <v>0.8251612186431885</v>
       </c>
       <c r="C33" s="1">
-        <v>340</v>
+        <v>398</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>340</v>
+        <v>398</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
@@ -3059,19 +3077,19 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="B34" s="2">
-        <v>0.7056387662887573</v>
+        <v>0.7339373230934143</v>
       </c>
       <c r="C34" s="1">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="D34" s="1">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="E34" s="1">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="F34" s="1">
         <v>0</v>
@@ -3080,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="1">
-        <v>0</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -3088,16 +3106,16 @@
         <v>40</v>
       </c>
       <c r="B35" s="2">
-        <v>0.6887372732162476</v>
+        <v>0.7049115896224976</v>
       </c>
       <c r="C35" s="1">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
       </c>
       <c r="E35" s="1">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="F35" s="1">
         <v>0</v>
@@ -3111,149 +3129,149 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="B36" s="2">
-        <v>0.6612722873687744</v>
+        <v>0.692471981048584</v>
       </c>
       <c r="C36" s="1">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="D36" s="1">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>292</v>
+        <v>334</v>
       </c>
       <c r="F36" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B37" s="2">
-        <v>0.6422580480575562</v>
+        <v>0.6489332914352417</v>
       </c>
       <c r="C37" s="1">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D37" s="1">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E37" s="1">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="F37" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="B38" s="2">
-        <v>0.6169057488441467</v>
+        <v>0.6302738785743713</v>
       </c>
       <c r="C38" s="1">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="D38" s="1">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="B39" s="2">
-        <v>0.5915534496307373</v>
+        <v>0.6053946614265442</v>
       </c>
       <c r="C39" s="1">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="D39" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E39" s="1">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>0.5725392699241638</v>
+        <v>0.580515444278717</v>
       </c>
       <c r="C40" s="1">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D40" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E40" s="1">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B41" s="2">
-        <v>0.5302854180335999</v>
+        <v>0.5618559718132019</v>
       </c>
       <c r="C41" s="1">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="D41" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E41" s="1">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -3262,30 +3280,30 @@
         <v>1</v>
       </c>
       <c r="H41" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B42" s="2">
-        <v>0.5028204321861267</v>
+        <v>0.5203906297683716</v>
       </c>
       <c r="C42" s="1">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="1">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -3296,16 +3314,16 @@
         <v>44</v>
       </c>
       <c r="B43" s="2">
-        <v>0.4859189093112946</v>
+        <v>0.4934380948543549</v>
       </c>
       <c r="C43" s="1">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -3322,16 +3340,16 @@
         <v>45</v>
       </c>
       <c r="B44" s="2">
-        <v>0.4816935360431671</v>
+        <v>0.4768519401550293</v>
       </c>
       <c r="C44" s="1">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
       </c>
       <c r="E44" s="1">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -3348,16 +3366,16 @@
         <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>0.4690173864364624</v>
+        <v>0.4727054238319397</v>
       </c>
       <c r="C45" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
       </c>
       <c r="E45" s="1">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -3374,16 +3392,16 @@
         <v>47</v>
       </c>
       <c r="B46" s="2">
-        <v>0.4183128178119659</v>
+        <v>0.4602657854557037</v>
       </c>
       <c r="C46" s="1">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
       </c>
       <c r="E46" s="1">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -3400,16 +3418,16 @@
         <v>48</v>
       </c>
       <c r="B47" s="2">
-        <v>0.3929605185985565</v>
+        <v>0.4105073213577271</v>
       </c>
       <c r="C47" s="1">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="D47" s="1">
         <v>0</v>
       </c>
       <c r="E47" s="1">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -3426,16 +3444,16 @@
         <v>49</v>
       </c>
       <c r="B48" s="2">
-        <v>0.2831005752086639</v>
+        <v>0.3856281042098999</v>
       </c>
       <c r="C48" s="1">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
       </c>
       <c r="E48" s="1">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -3452,16 +3470,16 @@
         <v>50</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2492975294589996</v>
+        <v>0.2778180837631226</v>
       </c>
       <c r="C49" s="1">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -3475,19 +3493,19 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="B50" s="2">
-        <v>0.245072141289711</v>
+        <v>0.2529388666152954</v>
       </c>
       <c r="C50" s="1">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E50" s="1">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -3496,24 +3514,24 @@
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="B51" s="2">
-        <v>0.2408467680215836</v>
+        <v>0.2446457892656326</v>
       </c>
       <c r="C51" s="1">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D51" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E51" s="1">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F51" s="1">
         <v>0</v>
@@ -3522,24 +3540,24 @@
         <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="B52" s="2">
-        <v>0.2323960065841675</v>
+        <v>0.2404992431402206</v>
       </c>
       <c r="C52" s="1">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E52" s="1">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F52" s="1">
         <v>0</v>
@@ -3548,24 +3566,24 @@
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="B53" s="2">
-        <v>0.2070437073707581</v>
+        <v>0.2363527119159699</v>
       </c>
       <c r="C53" s="1">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="D53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E53" s="1">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="F53" s="1">
         <v>0</v>
@@ -3574,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -3582,16 +3600,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.2070437073707581</v>
+        <v>0.2280596345663071</v>
       </c>
       <c r="C54" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="D54" s="1">
         <v>0</v>
       </c>
       <c r="E54" s="1">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="F54" s="1">
         <v>0</v>
@@ -3608,16 +3626,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.1816914230585098</v>
+        <v>0.2031804025173187</v>
       </c>
       <c r="C55" s="1">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D55" s="1">
         <v>0</v>
       </c>
       <c r="E55" s="1">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F55" s="1">
         <v>0</v>
@@ -3631,19 +3649,19 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.1352122128009796</v>
+        <v>0.2031804025173187</v>
       </c>
       <c r="C56" s="1">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D56" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="E56" s="1">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="F56" s="1">
         <v>0</v>
@@ -3652,24 +3670,24 @@
         <v>0</v>
       </c>
       <c r="H56" s="1">
-        <v>128</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1309868395328522</v>
+        <v>0.1783011704683304</v>
       </c>
       <c r="C57" s="1">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="D57" s="1">
         <v>0</v>
       </c>
       <c r="E57" s="1">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="F57" s="1">
         <v>0</v>
@@ -3683,19 +3701,19 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1183106899261475</v>
+        <v>0.1326892375946045</v>
       </c>
       <c r="C58" s="1">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D58" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E58" s="1">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F58" s="1">
         <v>0</v>
@@ -3704,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="1">
-        <v>0</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:8">
@@ -3712,16 +3730,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1098599284887314</v>
+        <v>0.1285427063703537</v>
       </c>
       <c r="C59" s="1">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D59" s="1">
         <v>0</v>
       </c>
       <c r="E59" s="1">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="F59" s="1">
         <v>0</v>
@@ -3738,16 +3756,16 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1056345477700234</v>
+        <v>0.1161030828952789</v>
       </c>
       <c r="C60" s="1">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D60" s="1">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F60" s="1">
         <v>0</v>
@@ -3764,16 +3782,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1014091670513153</v>
+        <v>0.1078100055456162</v>
       </c>
       <c r="C61" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D61" s="1">
         <v>0</v>
       </c>
       <c r="E61" s="1">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F61" s="1">
         <v>0</v>
@@ -3790,16 +3808,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.08450763672590256</v>
+        <v>0.1036634668707848</v>
       </c>
       <c r="C62" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D62" s="1">
         <v>0</v>
       </c>
       <c r="E62" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F62" s="1">
         <v>0</v>
@@ -3816,16 +3834,16 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.08028225600719452</v>
+        <v>0.09951692819595337</v>
       </c>
       <c r="C63" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D63" s="1">
         <v>0</v>
       </c>
       <c r="E63" s="1">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F63" s="1">
         <v>0</v>
@@ -3842,16 +3860,16 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>0.07605687528848648</v>
+        <v>0.08293077349662781</v>
       </c>
       <c r="C64" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D64" s="1">
         <v>0</v>
       </c>
       <c r="E64" s="1">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F64" s="1">
         <v>0</v>
@@ -3868,16 +3886,16 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.07605687528848648</v>
+        <v>0.07878423482179642</v>
       </c>
       <c r="C65" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D65" s="1">
         <v>0</v>
       </c>
       <c r="E65" s="1">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F65" s="1">
         <v>0</v>
@@ -3894,16 +3912,16 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.07183149456977844</v>
+        <v>0.07463769614696503</v>
       </c>
       <c r="C66" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D66" s="1">
         <v>0</v>
       </c>
       <c r="E66" s="1">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F66" s="1">
         <v>0</v>
@@ -3920,16 +3938,16 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.06760610640048981</v>
+        <v>0.07463769614696503</v>
       </c>
       <c r="C67" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
       </c>
       <c r="E67" s="1">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F67" s="1">
         <v>0</v>
@@ -3946,16 +3964,16 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>0.06338072568178177</v>
+        <v>0.07049115747213364</v>
       </c>
       <c r="C68" s="1">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
       </c>
       <c r="E68" s="1">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F68" s="1">
         <v>0</v>
@@ -3972,16 +3990,16 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>0.06338072568178177</v>
+        <v>0.06634461879730225</v>
       </c>
       <c r="C69" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
       </c>
       <c r="E69" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F69" s="1">
         <v>0</v>
@@ -3998,16 +4016,16 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>0.05915534496307373</v>
+        <v>0.06219808012247086</v>
       </c>
       <c r="C70" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
       </c>
       <c r="E70" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F70" s="1">
         <v>0</v>
@@ -4024,16 +4042,16 @@
         <v>69</v>
       </c>
       <c r="B71" s="2">
-        <v>0.05915534496307373</v>
+        <v>0.06219808012247086</v>
       </c>
       <c r="C71" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
       </c>
       <c r="E71" s="1">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F71" s="1">
         <v>0</v>
@@ -4050,16 +4068,16 @@
         <v>70</v>
       </c>
       <c r="B72" s="2">
-        <v>0.05492996424436569</v>
+        <v>0.05805154144763947</v>
       </c>
       <c r="C72" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
       </c>
       <c r="E72" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F72" s="1">
         <v>0</v>
@@ -4076,16 +4094,16 @@
         <v>71</v>
       </c>
       <c r="B73" s="2">
-        <v>0.03802843764424324</v>
+        <v>0.05805154144763947</v>
       </c>
       <c r="C73" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
       </c>
       <c r="E73" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F73" s="1">
         <v>0</v>
@@ -4102,16 +4120,16 @@
         <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>0.01690152660012245</v>
+        <v>0.05390500277280808</v>
       </c>
       <c r="C74" s="1">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
       </c>
       <c r="E74" s="1">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F74" s="1">
         <v>0</v>
@@ -4128,16 +4146,16 @@
         <v>73</v>
       </c>
       <c r="B75" s="2">
-        <v>0.01690152660012245</v>
+        <v>0.03731884807348251</v>
       </c>
       <c r="C75" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
       </c>
       <c r="E75" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F75" s="1">
         <v>0</v>
@@ -4154,16 +4172,16 @@
         <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>0.008450763300061226</v>
+        <v>0.01658615469932556</v>
       </c>
       <c r="C76" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
       </c>
       <c r="E76" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F76" s="1">
         <v>0</v>
@@ -4180,56 +4198,108 @@
         <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>0.008450763300061226</v>
+        <v>0.01658615469932556</v>
       </c>
       <c r="C77" s="1">
+        <v>8</v>
+      </c>
+      <c r="D77" s="1">
+        <v>0</v>
+      </c>
+      <c r="E77" s="1">
+        <v>8</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0</v>
+      </c>
+      <c r="G77" s="1">
+        <v>0</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B78" s="2">
+        <v>0.008293077349662781</v>
+      </c>
+      <c r="C78" s="1">
         <v>4</v>
       </c>
-      <c r="D77" s="1">
-        <v>0</v>
-      </c>
-      <c r="E77" s="1">
+      <c r="D78" s="1">
+        <v>0</v>
+      </c>
+      <c r="E78" s="1">
         <v>4</v>
       </c>
-      <c r="F77" s="1">
-        <v>0</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0</v>
-      </c>
-      <c r="H77" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
+      <c r="F78" s="1">
+        <v>0</v>
+      </c>
+      <c r="G78" s="1">
+        <v>0</v>
+      </c>
+      <c r="H78" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B78">
+      <c r="B79" s="2">
+        <v>0.008293077349662781</v>
+      </c>
+      <c r="C79" s="1">
+        <v>4</v>
+      </c>
+      <c r="D79" s="1">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1">
+        <v>4</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0</v>
+      </c>
+      <c r="G79" s="1">
+        <v>0</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C78">
+      <c r="C80">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D78">
+      <c r="D80">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E78">
+      <c r="E80">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F78">
+      <c r="F80">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G78">
+      <c r="G80">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H78">
+      <c r="H80">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/app/project/MDK_V5/AT32F403ARGT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F403ARGT7_WorkBench_analysis.xlsx
@@ -848,235 +848,235 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="78"/>
                 <c:pt idx="0">
-                  <c:v>11.63311386108398</c:v>
+                  <c:v>11.61112403869629</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.806564331054688</c:v>
+                  <c:v>9.809004783630371</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.114071369171143</c:v>
+                  <c:v>6.115592956542969</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.067070484161377</c:v>
+                  <c:v>5.068331241607666</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.639976978302002</c:v>
+                  <c:v>4.641131401062012</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.441627025604248</c:v>
+                  <c:v>3.44248366355896</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.242593288421631</c:v>
+                  <c:v>3.243400096893311</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.072585105895996</c:v>
+                  <c:v>3.073349714279175</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.989654302597046</c:v>
+                  <c:v>2.990398406982422</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.707689762115479</c:v>
+                  <c:v>2.70836353302002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.686957120895386</c:v>
+                  <c:v>2.687625646591187</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.595733165740967</c:v>
+                  <c:v>2.596379280090332</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.554267883300781</c:v>
+                  <c:v>2.554903507232666</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.334501266479492</c:v>
+                  <c:v>2.335082292556763</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.243277311325073</c:v>
+                  <c:v>2.243835687637329</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.118881225585938</c:v>
+                  <c:v>2.11940860748291</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.035950422286987</c:v>
+                  <c:v>2.036457061767578</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.961312770843506</c:v>
+                  <c:v>1.961800932884216</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.870088934898377</c:v>
+                  <c:v>1.870554327964783</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.662762045860291</c:v>
+                  <c:v>1.663175821304321</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.525926232337952</c:v>
+                  <c:v>1.526305913925171</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.501047015190125</c:v>
+                  <c:v>1.501420497894287</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.488607406616211</c:v>
+                  <c:v>1.488977789878845</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.264694333076477</c:v>
+                  <c:v>1.265009045600891</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.248108148574829</c:v>
+                  <c:v>1.248418688774109</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.248108148574829</c:v>
+                  <c:v>1.248418688774109</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.1568843126297</c:v>
+                  <c:v>1.157172203063965</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.078100085258484</c:v>
+                  <c:v>1.078368306159973</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.044927716255188</c:v>
+                  <c:v>1.045187830924988</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.8790662288665772</c:v>
+                  <c:v>0.8792849779129028</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.8251612186431885</c:v>
+                  <c:v>0.8253665566444397</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.7339373230934143</c:v>
+                  <c:v>0.7341200113296509</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.7049115896224976</c:v>
+                  <c:v>0.7050870060920715</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.692471981048584</c:v>
+                  <c:v>0.6926442980766296</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.6489332914352417</c:v>
+                  <c:v>0.649094820022583</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.6302738785743713</c:v>
+                  <c:v>0.6304306983947754</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.6053946614265442</c:v>
+                  <c:v>0.6055452823638916</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.580515444278717</c:v>
+                  <c:v>0.5806598663330078</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.5618559718132019</c:v>
+                  <c:v>0.561995804309845</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.5203906297683716</c:v>
+                  <c:v>0.5205200910568237</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.4934380948543549</c:v>
+                  <c:v>0.4935609102249146</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.4768519401550293</c:v>
+                  <c:v>0.4769706130027771</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.4727054238319397</c:v>
+                  <c:v>0.4728230535984039</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.4602657854557037</c:v>
+                  <c:v>0.460380345582962</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.4105073213577271</c:v>
+                  <c:v>0.4106094837188721</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.3856281042098999</c:v>
+                  <c:v>0.3857240676879883</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.2778180837631226</c:v>
+                  <c:v>0.277887225151062</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2529388666152954</c:v>
+                  <c:v>0.2530018091201782</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.2446457892656326</c:v>
+                  <c:v>0.2447066605091095</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.2404992431402206</c:v>
+                  <c:v>0.2405590862035751</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.2363527119159699</c:v>
+                  <c:v>0.236411526799202</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.2280596345663071</c:v>
+                  <c:v>0.2281163781881332</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.2031804025173187</c:v>
+                  <c:v>0.2032309621572495</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.2031804025173187</c:v>
+                  <c:v>0.2032309621572495</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1783011704683304</c:v>
+                  <c:v>0.1783455312252045</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1326892375946045</c:v>
+                  <c:v>0.1327222585678101</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1285427063703537</c:v>
+                  <c:v>0.1285746842622757</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1161030828952789</c:v>
+                  <c:v>0.1161319762468338</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1078100055456162</c:v>
+                  <c:v>0.1078368350863457</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1036634668707848</c:v>
+                  <c:v>0.1036892607808113</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.09951692819595337</c:v>
+                  <c:v>0.09954169392585754</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.08293077349662781</c:v>
+                  <c:v>0.08295141160488129</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.07878423482179642</c:v>
+                  <c:v>0.07880383729934692</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.07463769614696503</c:v>
+                  <c:v>0.07465627044439316</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.07463769614696503</c:v>
+                  <c:v>0.07465627044439316</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.07049115747213364</c:v>
+                  <c:v>0.0705086961388588</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.06634461879730225</c:v>
+                  <c:v>0.06636112928390503</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.06219808012247086</c:v>
+                  <c:v>0.06221355870366097</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.06219808012247086</c:v>
+                  <c:v>0.06221355870366097</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.05805154144763947</c:v>
+                  <c:v>0.0580659881234169</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.05805154144763947</c:v>
+                  <c:v>0.0580659881234169</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.05390500277280808</c:v>
+                  <c:v>0.05391841754317284</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.03731884807348251</c:v>
+                  <c:v>0.03732813522219658</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.01658615469932556</c:v>
+                  <c:v>0.01659028232097626</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.01658615469932556</c:v>
+                  <c:v>0.01659028232097626</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.008293077349662781</c:v>
+                  <c:v>0.008295141160488129</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.008293077349662781</c:v>
+                  <c:v>0.008295141160488129</c:v>
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>0</c:v>
@@ -1835,10 +1835,10 @@
         <v>70</v>
       </c>
       <c r="D14" s="1">
-        <v>5611</v>
+        <v>5599</v>
       </c>
       <c r="E14" s="1">
-        <v>5568</v>
+        <v>5556</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -2274,16 +2274,16 @@
         <v>12</v>
       </c>
       <c r="B3" s="2">
-        <v>11.63311386108398</v>
+        <v>11.61112403869629</v>
       </c>
       <c r="C3" s="1">
-        <v>5611</v>
+        <v>5599</v>
       </c>
       <c r="D3" s="1">
         <v>70</v>
       </c>
       <c r="E3" s="1">
-        <v>5568</v>
+        <v>5556</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -2300,7 +2300,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>9.806564331054688</v>
+        <v>9.809004783630371</v>
       </c>
       <c r="C4" s="1">
         <v>4730</v>
@@ -2326,7 +2326,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>6.114071369171143</v>
+        <v>6.115592956542969</v>
       </c>
       <c r="C5" s="1">
         <v>2949</v>
@@ -2352,7 +2352,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="2">
-        <v>5.067070484161377</v>
+        <v>5.068331241607666</v>
       </c>
       <c r="C6" s="1">
         <v>2444</v>
@@ -2378,7 +2378,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>4.639976978302002</v>
+        <v>4.641131401062012</v>
       </c>
       <c r="C7" s="1">
         <v>2238</v>
@@ -2404,7 +2404,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>3.441627025604248</v>
+        <v>3.44248366355896</v>
       </c>
       <c r="C8" s="1">
         <v>1660</v>
@@ -2430,7 +2430,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="2">
-        <v>3.242593288421631</v>
+        <v>3.243400096893311</v>
       </c>
       <c r="C9" s="1">
         <v>1564</v>
@@ -2456,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>3.072585105895996</v>
+        <v>3.073349714279175</v>
       </c>
       <c r="C10" s="1">
         <v>1482</v>
@@ -2482,7 +2482,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>2.989654302597046</v>
+        <v>2.990398406982422</v>
       </c>
       <c r="C11" s="1">
         <v>1442</v>
@@ -2508,7 +2508,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>2.707689762115479</v>
+        <v>2.70836353302002</v>
       </c>
       <c r="C12" s="1">
         <v>1306</v>
@@ -2534,7 +2534,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>2.686957120895386</v>
+        <v>2.687625646591187</v>
       </c>
       <c r="C13" s="1">
         <v>1296</v>
@@ -2560,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>2.595733165740967</v>
+        <v>2.596379280090332</v>
       </c>
       <c r="C14" s="1">
         <v>1252</v>
@@ -2586,7 +2586,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>2.554267883300781</v>
+        <v>2.554903507232666</v>
       </c>
       <c r="C15" s="1">
         <v>1232</v>
@@ -2612,7 +2612,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="2">
-        <v>2.334501266479492</v>
+        <v>2.335082292556763</v>
       </c>
       <c r="C16" s="1">
         <v>1126</v>
@@ -2638,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>2.243277311325073</v>
+        <v>2.243835687637329</v>
       </c>
       <c r="C17" s="1">
         <v>1082</v>
@@ -2664,7 +2664,7 @@
         <v>30</v>
       </c>
       <c r="B18" s="2">
-        <v>2.118881225585938</v>
+        <v>2.11940860748291</v>
       </c>
       <c r="C18" s="1">
         <v>1022</v>
@@ -2690,7 +2690,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>2.035950422286987</v>
+        <v>2.036457061767578</v>
       </c>
       <c r="C19" s="1">
         <v>982</v>
@@ -2716,7 +2716,7 @@
         <v>31</v>
       </c>
       <c r="B20" s="2">
-        <v>1.961312770843506</v>
+        <v>1.961800932884216</v>
       </c>
       <c r="C20" s="1">
         <v>946</v>
@@ -2742,7 +2742,7 @@
         <v>5</v>
       </c>
       <c r="B21" s="2">
-        <v>1.870088934898377</v>
+        <v>1.870554327964783</v>
       </c>
       <c r="C21" s="1">
         <v>902</v>
@@ -2768,7 +2768,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="2">
-        <v>1.662762045860291</v>
+        <v>1.663175821304321</v>
       </c>
       <c r="C22" s="1">
         <v>802</v>
@@ -2794,7 +2794,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>1.525926232337952</v>
+        <v>1.526305913925171</v>
       </c>
       <c r="C23" s="1">
         <v>736</v>
@@ -2820,7 +2820,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="2">
-        <v>1.501047015190125</v>
+        <v>1.501420497894287</v>
       </c>
       <c r="C24" s="1">
         <v>724</v>
@@ -2846,7 +2846,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2">
-        <v>1.488607406616211</v>
+        <v>1.488977789878845</v>
       </c>
       <c r="C25" s="1">
         <v>718</v>
@@ -2872,7 +2872,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="2">
-        <v>1.264694333076477</v>
+        <v>1.265009045600891</v>
       </c>
       <c r="C26" s="1">
         <v>610</v>
@@ -2898,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="2">
-        <v>1.248108148574829</v>
+        <v>1.248418688774109</v>
       </c>
       <c r="C27" s="1">
         <v>602</v>
@@ -2924,7 +2924,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="2">
-        <v>1.248108148574829</v>
+        <v>1.248418688774109</v>
       </c>
       <c r="C28" s="1">
         <v>602</v>
@@ -2950,7 +2950,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="2">
-        <v>1.1568843126297</v>
+        <v>1.157172203063965</v>
       </c>
       <c r="C29" s="1">
         <v>558</v>
@@ -2976,7 +2976,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="2">
-        <v>1.078100085258484</v>
+        <v>1.078368306159973</v>
       </c>
       <c r="C30" s="1">
         <v>520</v>
@@ -3002,7 +3002,7 @@
         <v>38</v>
       </c>
       <c r="B31" s="2">
-        <v>1.044927716255188</v>
+        <v>1.045187830924988</v>
       </c>
       <c r="C31" s="1">
         <v>504</v>
@@ -3028,7 +3028,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>0.8790662288665772</v>
+        <v>0.8792849779129028</v>
       </c>
       <c r="C32" s="1">
         <v>424</v>
@@ -3054,7 +3054,7 @@
         <v>39</v>
       </c>
       <c r="B33" s="2">
-        <v>0.8251612186431885</v>
+        <v>0.8253665566444397</v>
       </c>
       <c r="C33" s="1">
         <v>398</v>
@@ -3080,7 +3080,7 @@
         <v>8</v>
       </c>
       <c r="B34" s="2">
-        <v>0.7339373230934143</v>
+        <v>0.7341200113296509</v>
       </c>
       <c r="C34" s="1">
         <v>354</v>
@@ -3106,7 +3106,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="2">
-        <v>0.7049115896224976</v>
+        <v>0.7050870060920715</v>
       </c>
       <c r="C35" s="1">
         <v>340</v>
@@ -3132,7 +3132,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="2">
-        <v>0.692471981048584</v>
+        <v>0.6926442980766296</v>
       </c>
       <c r="C36" s="1">
         <v>334</v>
@@ -3158,7 +3158,7 @@
         <v>18</v>
       </c>
       <c r="B37" s="2">
-        <v>0.6489332914352417</v>
+        <v>0.649094820022583</v>
       </c>
       <c r="C37" s="1">
         <v>313</v>
@@ -3184,7 +3184,7 @@
         <v>42</v>
       </c>
       <c r="B38" s="2">
-        <v>0.6302738785743713</v>
+        <v>0.6304306983947754</v>
       </c>
       <c r="C38" s="1">
         <v>304</v>
@@ -3210,7 +3210,7 @@
         <v>19</v>
       </c>
       <c r="B39" s="2">
-        <v>0.6053946614265442</v>
+        <v>0.6055452823638916</v>
       </c>
       <c r="C39" s="1">
         <v>292</v>
@@ -3236,7 +3236,7 @@
         <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>0.580515444278717</v>
+        <v>0.5806598663330078</v>
       </c>
       <c r="C40" s="1">
         <v>280</v>
@@ -3262,7 +3262,7 @@
         <v>22</v>
       </c>
       <c r="B41" s="2">
-        <v>0.5618559718132019</v>
+        <v>0.561995804309845</v>
       </c>
       <c r="C41" s="1">
         <v>271</v>
@@ -3288,7 +3288,7 @@
         <v>24</v>
       </c>
       <c r="B42" s="2">
-        <v>0.5203906297683716</v>
+        <v>0.5205200910568237</v>
       </c>
       <c r="C42" s="1">
         <v>251</v>
@@ -3314,7 +3314,7 @@
         <v>44</v>
       </c>
       <c r="B43" s="2">
-        <v>0.4934380948543549</v>
+        <v>0.4935609102249146</v>
       </c>
       <c r="C43" s="1">
         <v>238</v>
@@ -3340,7 +3340,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="2">
-        <v>0.4768519401550293</v>
+        <v>0.4769706130027771</v>
       </c>
       <c r="C44" s="1">
         <v>230</v>
@@ -3366,7 +3366,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>0.4727054238319397</v>
+        <v>0.4728230535984039</v>
       </c>
       <c r="C45" s="1">
         <v>228</v>
@@ -3392,7 +3392,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="2">
-        <v>0.4602657854557037</v>
+        <v>0.460380345582962</v>
       </c>
       <c r="C46" s="1">
         <v>222</v>
@@ -3418,7 +3418,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2">
-        <v>0.4105073213577271</v>
+        <v>0.4106094837188721</v>
       </c>
       <c r="C47" s="1">
         <v>198</v>
@@ -3444,7 +3444,7 @@
         <v>49</v>
       </c>
       <c r="B48" s="2">
-        <v>0.3856281042098999</v>
+        <v>0.3857240676879883</v>
       </c>
       <c r="C48" s="1">
         <v>186</v>
@@ -3470,7 +3470,7 @@
         <v>50</v>
       </c>
       <c r="B49" s="2">
-        <v>0.2778180837631226</v>
+        <v>0.277887225151062</v>
       </c>
       <c r="C49" s="1">
         <v>134</v>
@@ -3496,7 +3496,7 @@
         <v>51</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2529388666152954</v>
+        <v>0.2530018091201782</v>
       </c>
       <c r="C50" s="1">
         <v>122</v>
@@ -3522,7 +3522,7 @@
         <v>52</v>
       </c>
       <c r="B51" s="2">
-        <v>0.2446457892656326</v>
+        <v>0.2447066605091095</v>
       </c>
       <c r="C51" s="1">
         <v>118</v>
@@ -3548,7 +3548,7 @@
         <v>25</v>
       </c>
       <c r="B52" s="2">
-        <v>0.2404992431402206</v>
+        <v>0.2405590862035751</v>
       </c>
       <c r="C52" s="1">
         <v>116</v>
@@ -3574,7 +3574,7 @@
         <v>20</v>
       </c>
       <c r="B53" s="2">
-        <v>0.2363527119159699</v>
+        <v>0.236411526799202</v>
       </c>
       <c r="C53" s="1">
         <v>114</v>
@@ -3600,7 +3600,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.2280596345663071</v>
+        <v>0.2281163781881332</v>
       </c>
       <c r="C54" s="1">
         <v>110</v>
@@ -3626,7 +3626,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.2031804025173187</v>
+        <v>0.2032309621572495</v>
       </c>
       <c r="C55" s="1">
         <v>98</v>
@@ -3652,7 +3652,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.2031804025173187</v>
+        <v>0.2032309621572495</v>
       </c>
       <c r="C56" s="1">
         <v>98</v>
@@ -3678,7 +3678,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1783011704683304</v>
+        <v>0.1783455312252045</v>
       </c>
       <c r="C57" s="1">
         <v>86</v>
@@ -3704,7 +3704,7 @@
         <v>9</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1326892375946045</v>
+        <v>0.1327222585678101</v>
       </c>
       <c r="C58" s="1">
         <v>64</v>
@@ -3730,7 +3730,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1285427063703537</v>
+        <v>0.1285746842622757</v>
       </c>
       <c r="C59" s="1">
         <v>62</v>
@@ -3756,7 +3756,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1161030828952789</v>
+        <v>0.1161319762468338</v>
       </c>
       <c r="C60" s="1">
         <v>56</v>
@@ -3782,7 +3782,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1078100055456162</v>
+        <v>0.1078368350863457</v>
       </c>
       <c r="C61" s="1">
         <v>52</v>
@@ -3808,7 +3808,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1036634668707848</v>
+        <v>0.1036892607808113</v>
       </c>
       <c r="C62" s="1">
         <v>50</v>
@@ -3834,7 +3834,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.09951692819595337</v>
+        <v>0.09954169392585754</v>
       </c>
       <c r="C63" s="1">
         <v>48</v>
@@ -3860,7 +3860,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>0.08293077349662781</v>
+        <v>0.08295141160488129</v>
       </c>
       <c r="C64" s="1">
         <v>40</v>
@@ -3886,7 +3886,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.07878423482179642</v>
+        <v>0.07880383729934692</v>
       </c>
       <c r="C65" s="1">
         <v>38</v>
@@ -3912,7 +3912,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.07463769614696503</v>
+        <v>0.07465627044439316</v>
       </c>
       <c r="C66" s="1">
         <v>36</v>
@@ -3938,7 +3938,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.07463769614696503</v>
+        <v>0.07465627044439316</v>
       </c>
       <c r="C67" s="1">
         <v>36</v>
@@ -3964,7 +3964,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>0.07049115747213364</v>
+        <v>0.0705086961388588</v>
       </c>
       <c r="C68" s="1">
         <v>34</v>
@@ -3990,7 +3990,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>0.06634461879730225</v>
+        <v>0.06636112928390503</v>
       </c>
       <c r="C69" s="1">
         <v>32</v>
@@ -4016,7 +4016,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>0.06219808012247086</v>
+        <v>0.06221355870366097</v>
       </c>
       <c r="C70" s="1">
         <v>30</v>
@@ -4042,7 +4042,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="2">
-        <v>0.06219808012247086</v>
+        <v>0.06221355870366097</v>
       </c>
       <c r="C71" s="1">
         <v>30</v>
@@ -4068,7 +4068,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="2">
-        <v>0.05805154144763947</v>
+        <v>0.0580659881234169</v>
       </c>
       <c r="C72" s="1">
         <v>28</v>
@@ -4094,7 +4094,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="2">
-        <v>0.05805154144763947</v>
+        <v>0.0580659881234169</v>
       </c>
       <c r="C73" s="1">
         <v>28</v>
@@ -4120,7 +4120,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>0.05390500277280808</v>
+        <v>0.05391841754317284</v>
       </c>
       <c r="C74" s="1">
         <v>26</v>
@@ -4146,7 +4146,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="2">
-        <v>0.03731884807348251</v>
+        <v>0.03732813522219658</v>
       </c>
       <c r="C75" s="1">
         <v>18</v>
@@ -4172,7 +4172,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>0.01658615469932556</v>
+        <v>0.01659028232097626</v>
       </c>
       <c r="C76" s="1">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>0.01658615469932556</v>
+        <v>0.01659028232097626</v>
       </c>
       <c r="C77" s="1">
         <v>8</v>
@@ -4224,7 +4224,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="2">
-        <v>0.008293077349662781</v>
+        <v>0.008295141160488129</v>
       </c>
       <c r="C78" s="1">
         <v>4</v>
@@ -4250,7 +4250,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2">
-        <v>0.008293077349662781</v>
+        <v>0.008295141160488129</v>
       </c>
       <c r="C79" s="1">
         <v>4</v>

--- a/app/project/MDK_V5/AT32F403ARGT7_WorkBench_analysis.xlsx
+++ b/app/project/MDK_V5/AT32F403ARGT7_WorkBench_analysis.xlsx
@@ -848,235 +848,235 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="78"/>
                 <c:pt idx="0">
-                  <c:v>11.61112403869629</c:v>
+                  <c:v>11.58517646789551</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.809004783630371</c:v>
+                  <c:v>9.753977775573731</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>6.115592956542969</c:v>
+                  <c:v>6.358500957489014</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.068331241607666</c:v>
+                  <c:v>5.057004928588867</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.641131401062012</c:v>
+                  <c:v>4.630760192871094</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.44248366355896</c:v>
+                  <c:v>3.43479061126709</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.243400096893311</c:v>
+                  <c:v>3.236152172088623</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.073349714279175</c:v>
+                  <c:v>3.066481828689575</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.990398406982422</c:v>
+                  <c:v>2.983715772628784</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.70836353302002</c:v>
+                  <c:v>2.702311277389526</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.687625646591187</c:v>
+                  <c:v>2.681619644165039</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.596379280090332</c:v>
+                  <c:v>2.590577125549316</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.554903507232666</c:v>
+                  <c:v>2.549194097518921</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.335082292556763</c:v>
+                  <c:v>2.329864025115967</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.243835687637329</c:v>
+                  <c:v>2.238821506500244</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.11940860748291</c:v>
+                  <c:v>2.114672422409058</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.036457061767578</c:v>
+                  <c:v>2.031906366348267</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.961800932884216</c:v>
+                  <c:v>1.957416892051697</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.870554327964783</c:v>
+                  <c:v>1.866374254226685</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.663175821304321</c:v>
+                  <c:v>1.659459114074707</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.526305913925171</c:v>
+                  <c:v>1.522895097732544</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.501420497894287</c:v>
+                  <c:v>1.49806535243988</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.488977789878845</c:v>
+                  <c:v>1.485650420188904</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.265009045600891</c:v>
+                  <c:v>1.262182116508484</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.248418688774109</c:v>
+                  <c:v>1.245628952980042</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.248418688774109</c:v>
+                  <c:v>1.245628952980042</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.157172203063965</c:v>
+                  <c:v>1.154586315155029</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.078368306159973</c:v>
+                  <c:v>1.075958490371704</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>1.045187830924988</c:v>
+                  <c:v>1.042852163314819</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.8792849779129028</c:v>
+                  <c:v>0.8773200511932373</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.8253665566444397</c:v>
+                  <c:v>0.8235220909118652</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.7341200113296509</c:v>
+                  <c:v>0.732479453086853</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.7050870060920715</c:v>
+                  <c:v>0.7035113573074341</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.6926442980766296</c:v>
+                  <c:v>0.6910964250564575</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.649094820022583</c:v>
+                  <c:v>0.6476442813873291</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.6304306983947754</c:v>
+                  <c:v>0.6290218830108643</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.6055452823638916</c:v>
+                  <c:v>0.6041920781135559</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.5806598663330078</c:v>
+                  <c:v>0.5793622732162476</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.561995804309845</c:v>
+                  <c:v>0.5607399344444275</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.5205200910568237</c:v>
+                  <c:v>0.519356906414032</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.4935609102249146</c:v>
+                  <c:v>0.4924579560756683</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.4769706130027771</c:v>
+                  <c:v>0.4759047329425812</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.4728230535984039</c:v>
+                  <c:v>0.4717664420604706</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.460380345582962</c:v>
+                  <c:v>0.4593515396118164</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.4106094837188721</c:v>
+                  <c:v>0.4096919000148773</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.3857240676879883</c:v>
+                  <c:v>0.384862095117569</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.277887225151062</c:v>
+                  <c:v>0.2772662341594696</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.2530018091201782</c:v>
+                  <c:v>0.2524364292621613</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.2447066605091095</c:v>
+                  <c:v>0.2441598176956177</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.2405590862035751</c:v>
+                  <c:v>0.2400215119123459</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.236411526799202</c:v>
+                  <c:v>0.2358832210302353</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.2281163781881332</c:v>
+                  <c:v>0.2276066094636917</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.2032309621572495</c:v>
+                  <c:v>0.2027768045663834</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.2032309621572495</c:v>
+                  <c:v>0.2027768045663834</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.1783455312252045</c:v>
+                  <c:v>0.1779469847679138</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.1327222585678101</c:v>
+                  <c:v>0.1324256658554077</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.1285746842622757</c:v>
+                  <c:v>0.1282873600721359</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.1161319762468338</c:v>
+                  <c:v>0.1158724576234818</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.1078368350863457</c:v>
+                  <c:v>0.1075958535075188</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.1036892607808113</c:v>
+                  <c:v>0.103457547724247</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.09954169392585754</c:v>
+                  <c:v>0.09931924939155579</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.08295141160488129</c:v>
+                  <c:v>0.08276604115962982</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.07880383729934692</c:v>
+                  <c:v>0.07862773537635803</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.07465627044439316</c:v>
+                  <c:v>0.07448943704366684</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.07465627044439316</c:v>
+                  <c:v>0.07448943704366684</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.0705086961388588</c:v>
+                  <c:v>0.07035113126039505</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.06636112928390503</c:v>
+                  <c:v>0.06621283292770386</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.06221355870366097</c:v>
+                  <c:v>0.06207453086972237</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.06221355870366097</c:v>
+                  <c:v>0.06207453086972237</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.0580659881234169</c:v>
+                  <c:v>0.05793622881174088</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.0580659881234169</c:v>
+                  <c:v>0.05793622881174088</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.05391841754317284</c:v>
+                  <c:v>0.05379792675375938</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.03732813522219658</c:v>
+                  <c:v>0.03724471852183342</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.01659028232097626</c:v>
+                  <c:v>0.01655320823192596</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.01659028232097626</c:v>
+                  <c:v>0.01655320823192596</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.008295141160488129</c:v>
+                  <c:v>0.008276604115962982</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.008295141160488129</c:v>
+                  <c:v>0.008276604115962982</c:v>
                 </c:pt>
                 <c:pt idx="77">
                   <c:v>0</c:v>
@@ -1679,10 +1679,10 @@
         <v>194</v>
       </c>
       <c r="D8" s="1">
-        <v>2949</v>
+        <v>3073</v>
       </c>
       <c r="E8" s="1">
-        <v>2758</v>
+        <v>2882</v>
       </c>
       <c r="F8" s="1">
         <v>0</v>
@@ -1861,10 +1861,10 @@
         <v>58</v>
       </c>
       <c r="D15" s="1">
-        <v>4730</v>
+        <v>4714</v>
       </c>
       <c r="E15" s="1">
-        <v>4730</v>
+        <v>4714</v>
       </c>
       <c r="F15" s="1">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2">
-        <v>11.61112403869629</v>
+        <v>11.58517646789551</v>
       </c>
       <c r="C3" s="1">
         <v>5599</v>
@@ -2300,16 +2300,16 @@
         <v>13</v>
       </c>
       <c r="B4" s="2">
-        <v>9.809004783630371</v>
+        <v>9.753977775573731</v>
       </c>
       <c r="C4" s="1">
-        <v>4730</v>
+        <v>4714</v>
       </c>
       <c r="D4" s="1">
         <v>58</v>
       </c>
       <c r="E4" s="1">
-        <v>4730</v>
+        <v>4714</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -2326,16 +2326,16 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>6.115592956542969</v>
+        <v>6.358500957489014</v>
       </c>
       <c r="C5" s="1">
-        <v>2949</v>
+        <v>3073</v>
       </c>
       <c r="D5" s="1">
         <v>194</v>
       </c>
       <c r="E5" s="1">
-        <v>2758</v>
+        <v>2882</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
@@ -2352,7 +2352,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="2">
-        <v>5.068331241607666</v>
+        <v>5.057004928588867</v>
       </c>
       <c r="C6" s="1">
         <v>2444</v>
@@ -2378,7 +2378,7 @@
         <v>17</v>
       </c>
       <c r="B7" s="2">
-        <v>4.641131401062012</v>
+        <v>4.630760192871094</v>
       </c>
       <c r="C7" s="1">
         <v>2238</v>
@@ -2404,7 +2404,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="2">
-        <v>3.44248366355896</v>
+        <v>3.43479061126709</v>
       </c>
       <c r="C8" s="1">
         <v>1660</v>
@@ -2430,7 +2430,7 @@
         <v>26</v>
       </c>
       <c r="B9" s="2">
-        <v>3.243400096893311</v>
+        <v>3.236152172088623</v>
       </c>
       <c r="C9" s="1">
         <v>1564</v>
@@ -2456,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2">
-        <v>3.073349714279175</v>
+        <v>3.066481828689575</v>
       </c>
       <c r="C10" s="1">
         <v>1482</v>
@@ -2482,7 +2482,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="2">
-        <v>2.990398406982422</v>
+        <v>2.983715772628784</v>
       </c>
       <c r="C11" s="1">
         <v>1442</v>
@@ -2508,7 +2508,7 @@
         <v>28</v>
       </c>
       <c r="B12" s="2">
-        <v>2.70836353302002</v>
+        <v>2.702311277389526</v>
       </c>
       <c r="C12" s="1">
         <v>1306</v>
@@ -2534,7 +2534,7 @@
         <v>29</v>
       </c>
       <c r="B13" s="2">
-        <v>2.687625646591187</v>
+        <v>2.681619644165039</v>
       </c>
       <c r="C13" s="1">
         <v>1296</v>
@@ -2560,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>2.596379280090332</v>
+        <v>2.590577125549316</v>
       </c>
       <c r="C14" s="1">
         <v>1252</v>
@@ -2586,7 +2586,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>2.554903507232666</v>
+        <v>2.549194097518921</v>
       </c>
       <c r="C15" s="1">
         <v>1232</v>
@@ -2612,7 +2612,7 @@
         <v>7</v>
       </c>
       <c r="B16" s="2">
-        <v>2.335082292556763</v>
+        <v>2.329864025115967</v>
       </c>
       <c r="C16" s="1">
         <v>1126</v>
@@ -2638,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>2.243835687637329</v>
+        <v>2.238821506500244</v>
       </c>
       <c r="C17" s="1">
         <v>1082</v>
@@ -2664,7 +2664,7 @@
         <v>30</v>
       </c>
       <c r="B18" s="2">
-        <v>2.11940860748291</v>
+        <v>2.114672422409058</v>
       </c>
       <c r="C18" s="1">
         <v>1022</v>
@@ -2690,7 +2690,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="2">
-        <v>2.036457061767578</v>
+        <v>2.031906366348267</v>
       </c>
       <c r="C19" s="1">
         <v>982</v>
@@ -2716,7 +2716,7 @@
         <v>31</v>
       </c>
       <c r="B20" s="2">
-        <v>1.961800932884216</v>
+        <v>1.957416892051697</v>
       </c>
       <c r="C20" s="1">
         <v>946</v>
@@ -2742,7 +2742,7 @@
         <v>5</v>
       </c>
       <c r="B21" s="2">
-        <v>1.870554327964783</v>
+        <v>1.866374254226685</v>
       </c>
       <c r="C21" s="1">
         <v>902</v>
@@ -2768,7 +2768,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="2">
-        <v>1.663175821304321</v>
+        <v>1.659459114074707</v>
       </c>
       <c r="C22" s="1">
         <v>802</v>
@@ -2794,7 +2794,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2">
-        <v>1.526305913925171</v>
+        <v>1.522895097732544</v>
       </c>
       <c r="C23" s="1">
         <v>736</v>
@@ -2820,7 +2820,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="2">
-        <v>1.501420497894287</v>
+        <v>1.49806535243988</v>
       </c>
       <c r="C24" s="1">
         <v>724</v>
@@ -2846,7 +2846,7 @@
         <v>34</v>
       </c>
       <c r="B25" s="2">
-        <v>1.488977789878845</v>
+        <v>1.485650420188904</v>
       </c>
       <c r="C25" s="1">
         <v>718</v>
@@ -2872,7 +2872,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="2">
-        <v>1.265009045600891</v>
+        <v>1.262182116508484</v>
       </c>
       <c r="C26" s="1">
         <v>610</v>
@@ -2898,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="2">
-        <v>1.248418688774109</v>
+        <v>1.245628952980042</v>
       </c>
       <c r="C27" s="1">
         <v>602</v>
@@ -2924,7 +2924,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="2">
-        <v>1.248418688774109</v>
+        <v>1.245628952980042</v>
       </c>
       <c r="C28" s="1">
         <v>602</v>
@@ -2950,7 +2950,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="2">
-        <v>1.157172203063965</v>
+        <v>1.154586315155029</v>
       </c>
       <c r="C29" s="1">
         <v>558</v>
@@ -2976,7 +2976,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="2">
-        <v>1.078368306159973</v>
+        <v>1.075958490371704</v>
       </c>
       <c r="C30" s="1">
         <v>520</v>
@@ -3002,7 +3002,7 @@
         <v>38</v>
       </c>
       <c r="B31" s="2">
-        <v>1.045187830924988</v>
+        <v>1.042852163314819</v>
       </c>
       <c r="C31" s="1">
         <v>504</v>
@@ -3028,7 +3028,7 @@
         <v>4</v>
       </c>
       <c r="B32" s="2">
-        <v>0.8792849779129028</v>
+        <v>0.8773200511932373</v>
       </c>
       <c r="C32" s="1">
         <v>424</v>
@@ -3054,7 +3054,7 @@
         <v>39</v>
       </c>
       <c r="B33" s="2">
-        <v>0.8253665566444397</v>
+        <v>0.8235220909118652</v>
       </c>
       <c r="C33" s="1">
         <v>398</v>
@@ -3080,7 +3080,7 @@
         <v>8</v>
       </c>
       <c r="B34" s="2">
-        <v>0.7341200113296509</v>
+        <v>0.732479453086853</v>
       </c>
       <c r="C34" s="1">
         <v>354</v>
@@ -3106,7 +3106,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="2">
-        <v>0.7050870060920715</v>
+        <v>0.7035113573074341</v>
       </c>
       <c r="C35" s="1">
         <v>340</v>
@@ -3132,7 +3132,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="2">
-        <v>0.6926442980766296</v>
+        <v>0.6910964250564575</v>
       </c>
       <c r="C36" s="1">
         <v>334</v>
@@ -3158,7 +3158,7 @@
         <v>18</v>
       </c>
       <c r="B37" s="2">
-        <v>0.649094820022583</v>
+        <v>0.6476442813873291</v>
       </c>
       <c r="C37" s="1">
         <v>313</v>
@@ -3184,7 +3184,7 @@
         <v>42</v>
       </c>
       <c r="B38" s="2">
-        <v>0.6304306983947754</v>
+        <v>0.6290218830108643</v>
       </c>
       <c r="C38" s="1">
         <v>304</v>
@@ -3210,7 +3210,7 @@
         <v>19</v>
       </c>
       <c r="B39" s="2">
-        <v>0.6055452823638916</v>
+        <v>0.6041920781135559</v>
       </c>
       <c r="C39" s="1">
         <v>292</v>
@@ -3236,7 +3236,7 @@
         <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>0.5806598663330078</v>
+        <v>0.5793622732162476</v>
       </c>
       <c r="C40" s="1">
         <v>280</v>
@@ -3262,7 +3262,7 @@
         <v>22</v>
       </c>
       <c r="B41" s="2">
-        <v>0.561995804309845</v>
+        <v>0.5607399344444275</v>
       </c>
       <c r="C41" s="1">
         <v>271</v>
@@ -3288,7 +3288,7 @@
         <v>24</v>
       </c>
       <c r="B42" s="2">
-        <v>0.5205200910568237</v>
+        <v>0.519356906414032</v>
       </c>
       <c r="C42" s="1">
         <v>251</v>
@@ -3314,7 +3314,7 @@
         <v>44</v>
       </c>
       <c r="B43" s="2">
-        <v>0.4935609102249146</v>
+        <v>0.4924579560756683</v>
       </c>
       <c r="C43" s="1">
         <v>238</v>
@@ -3340,7 +3340,7 @@
         <v>45</v>
       </c>
       <c r="B44" s="2">
-        <v>0.4769706130027771</v>
+        <v>0.4759047329425812</v>
       </c>
       <c r="C44" s="1">
         <v>230</v>
@@ -3366,7 +3366,7 @@
         <v>46</v>
       </c>
       <c r="B45" s="2">
-        <v>0.4728230535984039</v>
+        <v>0.4717664420604706</v>
       </c>
       <c r="C45" s="1">
         <v>228</v>
@@ -3392,7 +3392,7 @@
         <v>47</v>
       </c>
       <c r="B46" s="2">
-        <v>0.460380345582962</v>
+        <v>0.4593515396118164</v>
       </c>
       <c r="C46" s="1">
         <v>222</v>
@@ -3418,7 +3418,7 @@
         <v>48</v>
       </c>
       <c r="B47" s="2">
-        <v>0.4106094837188721</v>
+        <v>0.4096919000148773</v>
       </c>
       <c r="C47" s="1">
         <v>198</v>
@@ -3444,7 +3444,7 @@
         <v>49</v>
       </c>
       <c r="B48" s="2">
-        <v>0.3857240676879883</v>
+        <v>0.384862095117569</v>
       </c>
       <c r="C48" s="1">
         <v>186</v>
@@ -3470,7 +3470,7 @@
         <v>50</v>
       </c>
       <c r="B49" s="2">
-        <v>0.277887225151062</v>
+        <v>0.2772662341594696</v>
       </c>
       <c r="C49" s="1">
         <v>134</v>
@@ -3496,7 +3496,7 @@
         <v>51</v>
       </c>
       <c r="B50" s="2">
-        <v>0.2530018091201782</v>
+        <v>0.2524364292621613</v>
       </c>
       <c r="C50" s="1">
         <v>122</v>
@@ -3522,7 +3522,7 @@
         <v>52</v>
       </c>
       <c r="B51" s="2">
-        <v>0.2447066605091095</v>
+        <v>0.2441598176956177</v>
       </c>
       <c r="C51" s="1">
         <v>118</v>
@@ -3548,7 +3548,7 @@
         <v>25</v>
       </c>
       <c r="B52" s="2">
-        <v>0.2405590862035751</v>
+        <v>0.2400215119123459</v>
       </c>
       <c r="C52" s="1">
         <v>116</v>
@@ -3574,7 +3574,7 @@
         <v>20</v>
       </c>
       <c r="B53" s="2">
-        <v>0.236411526799202</v>
+        <v>0.2358832210302353</v>
       </c>
       <c r="C53" s="1">
         <v>114</v>
@@ -3600,7 +3600,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="2">
-        <v>0.2281163781881332</v>
+        <v>0.2276066094636917</v>
       </c>
       <c r="C54" s="1">
         <v>110</v>
@@ -3626,7 +3626,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="2">
-        <v>0.2032309621572495</v>
+        <v>0.2027768045663834</v>
       </c>
       <c r="C55" s="1">
         <v>98</v>
@@ -3652,7 +3652,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="2">
-        <v>0.2032309621572495</v>
+        <v>0.2027768045663834</v>
       </c>
       <c r="C56" s="1">
         <v>98</v>
@@ -3678,7 +3678,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2">
-        <v>0.1783455312252045</v>
+        <v>0.1779469847679138</v>
       </c>
       <c r="C57" s="1">
         <v>86</v>
@@ -3704,7 +3704,7 @@
         <v>9</v>
       </c>
       <c r="B58" s="2">
-        <v>0.1327222585678101</v>
+        <v>0.1324256658554077</v>
       </c>
       <c r="C58" s="1">
         <v>64</v>
@@ -3730,7 +3730,7 @@
         <v>57</v>
       </c>
       <c r="B59" s="2">
-        <v>0.1285746842622757</v>
+        <v>0.1282873600721359</v>
       </c>
       <c r="C59" s="1">
         <v>62</v>
@@ -3756,7 +3756,7 @@
         <v>58</v>
       </c>
       <c r="B60" s="2">
-        <v>0.1161319762468338</v>
+        <v>0.1158724576234818</v>
       </c>
       <c r="C60" s="1">
         <v>56</v>
@@ -3782,7 +3782,7 @@
         <v>59</v>
       </c>
       <c r="B61" s="2">
-        <v>0.1078368350863457</v>
+        <v>0.1075958535075188</v>
       </c>
       <c r="C61" s="1">
         <v>52</v>
@@ -3808,7 +3808,7 @@
         <v>60</v>
       </c>
       <c r="B62" s="2">
-        <v>0.1036892607808113</v>
+        <v>0.103457547724247</v>
       </c>
       <c r="C62" s="1">
         <v>50</v>
@@ -3834,7 +3834,7 @@
         <v>61</v>
       </c>
       <c r="B63" s="2">
-        <v>0.09954169392585754</v>
+        <v>0.09931924939155579</v>
       </c>
       <c r="C63" s="1">
         <v>48</v>
@@ -3860,7 +3860,7 @@
         <v>62</v>
       </c>
       <c r="B64" s="2">
-        <v>0.08295141160488129</v>
+        <v>0.08276604115962982</v>
       </c>
       <c r="C64" s="1">
         <v>40</v>
@@ -3886,7 +3886,7 @@
         <v>63</v>
       </c>
       <c r="B65" s="2">
-        <v>0.07880383729934692</v>
+        <v>0.07862773537635803</v>
       </c>
       <c r="C65" s="1">
         <v>38</v>
@@ -3912,7 +3912,7 @@
         <v>64</v>
       </c>
       <c r="B66" s="2">
-        <v>0.07465627044439316</v>
+        <v>0.07448943704366684</v>
       </c>
       <c r="C66" s="1">
         <v>36</v>
@@ -3938,7 +3938,7 @@
         <v>65</v>
       </c>
       <c r="B67" s="2">
-        <v>0.07465627044439316</v>
+        <v>0.07448943704366684</v>
       </c>
       <c r="C67" s="1">
         <v>36</v>
@@ -3964,7 +3964,7 @@
         <v>66</v>
       </c>
       <c r="B68" s="2">
-        <v>0.0705086961388588</v>
+        <v>0.07035113126039505</v>
       </c>
       <c r="C68" s="1">
         <v>34</v>
@@ -3990,7 +3990,7 @@
         <v>67</v>
       </c>
       <c r="B69" s="2">
-        <v>0.06636112928390503</v>
+        <v>0.06621283292770386</v>
       </c>
       <c r="C69" s="1">
         <v>32</v>
@@ -4016,7 +4016,7 @@
         <v>68</v>
       </c>
       <c r="B70" s="2">
-        <v>0.06221355870366097</v>
+        <v>0.06207453086972237</v>
       </c>
       <c r="C70" s="1">
         <v>30</v>
@@ -4042,7 +4042,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="2">
-        <v>0.06221355870366097</v>
+        <v>0.06207453086972237</v>
       </c>
       <c r="C71" s="1">
         <v>30</v>
@@ -4068,7 +4068,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="2">
-        <v>0.0580659881234169</v>
+        <v>0.05793622881174088</v>
       </c>
       <c r="C72" s="1">
         <v>28</v>
@@ -4094,7 +4094,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="2">
-        <v>0.0580659881234169</v>
+        <v>0.05793622881174088</v>
       </c>
       <c r="C73" s="1">
         <v>28</v>
@@ -4120,7 +4120,7 @@
         <v>72</v>
       </c>
       <c r="B74" s="2">
-        <v>0.05391841754317284</v>
+        <v>0.05379792675375938</v>
       </c>
       <c r="C74" s="1">
         <v>26</v>
@@ -4146,7 +4146,7 @@
         <v>73</v>
       </c>
       <c r="B75" s="2">
-        <v>0.03732813522219658</v>
+        <v>0.03724471852183342</v>
       </c>
       <c r="C75" s="1">
         <v>18</v>
@@ -4172,7 +4172,7 @@
         <v>74</v>
       </c>
       <c r="B76" s="2">
-        <v>0.01659028232097626</v>
+        <v>0.01655320823192596</v>
       </c>
       <c r="C76" s="1">
         <v>8</v>
@@ -4198,7 +4198,7 @@
         <v>75</v>
       </c>
       <c r="B77" s="2">
-        <v>0.01659028232097626</v>
+        <v>0.01655320823192596</v>
       </c>
       <c r="C77" s="1">
         <v>8</v>
@@ -4224,7 +4224,7 @@
         <v>76</v>
       </c>
       <c r="B78" s="2">
-        <v>0.008295141160488129</v>
+        <v>0.008276604115962982</v>
       </c>
       <c r="C78" s="1">
         <v>4</v>
@@ -4250,7 +4250,7 @@
         <v>77</v>
       </c>
       <c r="B79" s="2">
-        <v>0.008295141160488129</v>
+        <v>0.008276604115962982</v>
       </c>
       <c r="C79" s="1">
         <v>4</v>
